--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F948795-5009-4B29-B979-C74BE1BD8107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7315F0BB-E686-4672-9228-4A9C63B056AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33405" yWindow="1665" windowWidth="21600" windowHeight="12525" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31350" yWindow="1500" windowWidth="21600" windowHeight="12525" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -291,9 +291,6 @@
     <t>c_inv_musd_per_gw_per_yr</t>
   </si>
   <si>
-    <t>f_hold_musd_per_gw_per_yr</t>
-  </si>
-  <si>
     <t>g_exp_ub_per_yr</t>
   </si>
   <si>
@@ -356,6 +353,9 @@
 - capacities and demand caps: gw
 - investment / holding costs: musd_per_gw_per_yr
 </t>
+  </si>
+  <si>
+    <t>c_hold_musd_per_gw_per_yr</t>
   </si>
 </sst>
 </file>
@@ -629,6 +629,222 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F950EA5-5C9E-07B9-A431-6203687B16CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF077932-AB85-5284-F139-1A17DAC5BD2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A28031-2919-2EBA-1038-0AB0ED981ED7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AFB1342-4107-852A-346B-EF7E40FB286A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -994,49 +1210,49 @@
         <v>32</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
@@ -1072,7 +1288,7 @@
         <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1000</v>
@@ -1152,7 +1368,7 @@
         <v>0.5</v>
       </c>
       <c r="K3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>1000</v>
@@ -1232,7 +1448,7 @@
         <v>0.5</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1000</v>
@@ -1312,7 +1528,7 @@
         <v>0.5</v>
       </c>
       <c r="K5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1000</v>
@@ -1392,7 +1608,7 @@
         <v>0.5</v>
       </c>
       <c r="K6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>1000</v>
@@ -1472,7 +1688,7 @@
         <v>0.5</v>
       </c>
       <c r="K7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>1000</v>
@@ -1553,7 +1769,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -1724,12 +1940,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7315F0BB-E686-4672-9228-4A9C63B056AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA701123-2A11-4AC9-B570-836E1DCDEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31350" yWindow="1500" windowWidth="21600" windowHeight="12525" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30030" yWindow="2010" windowWidth="21600" windowHeight="12525" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>setting</t>
   </si>
@@ -289,9 +289,6 @@
   </si>
   <si>
     <t>c_inv_musd_per_gw_per_yr</t>
-  </si>
-  <si>
-    <t>g_exp_ub_per_yr</t>
   </si>
   <si>
     <t>g_dec_ub_per_yr</t>
@@ -356,6 +353,12 @@
   </si>
   <si>
     <t>c_hold_musd_per_gw_per_yr</t>
+  </si>
+  <si>
+    <t>roa</t>
+  </si>
+  <si>
+    <t>g_exp_ub_per_yr_gw</t>
   </si>
 </sst>
 </file>
@@ -845,6 +848,222 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3361DFC-9C6A-3512-24A2-CB9D19AE59B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9610934A-61E7-AFCD-A513-99981C840CF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{602025C5-2E30-3980-7139-BCA302E673FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E08AE79-14AE-B6A1-136A-B86C4FF1DC6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1210,49 +1429,49 @@
         <v>32</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
@@ -1285,7 +1504,7 @@
         <v>2.5</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>27.4</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1365,7 +1584,7 @@
         <v>8.75</v>
       </c>
       <c r="J3">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1420,7 +1639,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>38.270000000000003</v>
@@ -1445,7 +1664,7 @@
         <v>8.75</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>14.5</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1497,7 +1716,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>110</v>
@@ -1525,7 +1744,7 @@
         <v>2.875</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>3.2479999999999989</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1605,7 +1824,7 @@
         <v>7.5</v>
       </c>
       <c r="J6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1685,7 +1904,7 @@
         <v>6.25</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>8.6799999999999962</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1741,7 +1960,34 @@
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="13" spans="1:23" ht="30.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:23" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
     <row r="24" spans="18:22" x14ac:dyDescent="0.35">
       <c r="R24" s="3"/>
     </row>
@@ -1769,7 +2015,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -1940,12 +2186,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA701123-2A11-4AC9-B570-836E1DCDEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09D3F73-E1D3-47E1-9704-FADEA509A785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30030" yWindow="2010" windowWidth="21600" windowHeight="12525" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$W$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$Y$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{3BD3B233-C8F3-4C4E-A8E9-4D00AB9FAA5A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -143,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +185,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2040 = p_full/(eps_abs_base*dmax_2040). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{2C5B7B49-3F16-4D84-B7A7-EAEBC7F68F01}">
       <text>
         <r>
           <rPr>
@@ -190,7 +218,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>setting</t>
   </si>
@@ -359,6 +387,15 @@
   </si>
   <si>
     <t>g_exp_ub_per_yr_gw</t>
+  </si>
+  <si>
+    <t>b_dem_2045_usd_per_kw_per_gw</t>
+  </si>
+  <si>
+    <t>a_dem_2045_usd_per_kw</t>
+  </si>
+  <si>
+    <t>dmax_2045_gw</t>
   </si>
 </sst>
 </file>
@@ -458,7 +495,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -483,7 +520,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -532,7 +569,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -586,7 +623,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -640,7 +677,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -694,7 +731,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -748,7 +785,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -802,7 +839,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -856,7 +893,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -910,7 +947,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -964,7 +1001,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -1018,7 +1055,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -1040,6 +1077,60 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="8299450" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F95148C-FA07-E8BD-33E4-E4A856624368}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8296275" cy="6353175"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1244,9 +1335,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,12 +1345,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1267,37 +1358,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1310,9 +1401,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1320,7 +1411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1328,7 +1419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1336,7 +1427,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1344,7 +1435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1352,7 +1443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1360,7 +1451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1375,35 +1466,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W26"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.7265625" customWidth="1"/>
-    <col min="5" max="5" width="20.26953125" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
-    <col min="7" max="7" width="25.7265625" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="30.6328125" customWidth="1"/>
-    <col min="10" max="10" width="20.36328125" customWidth="1"/>
-    <col min="11" max="11" width="23.08984375" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="13" width="16.54296875" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="27.90625" customWidth="1"/>
-    <col min="16" max="16" width="25.36328125" customWidth="1"/>
-    <col min="17" max="17" width="24.1796875" customWidth="1"/>
-    <col min="18" max="18" width="22.90625" customWidth="1"/>
-    <col min="19" max="19" width="28.6328125" customWidth="1"/>
-    <col min="20" max="20" width="34.6328125" customWidth="1"/>
-    <col min="21" max="21" width="31.90625" customWidth="1"/>
-    <col min="22" max="22" width="31.36328125" customWidth="1"/>
-    <col min="23" max="23" width="30.7265625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="30.5703125" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="27.85546875" customWidth="1"/>
+    <col min="17" max="17" width="25.42578125" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="28.5703125" customWidth="1"/>
+    <col min="21" max="21" width="34.5703125" customWidth="1"/>
+    <col min="22" max="22" width="31.85546875" customWidth="1"/>
+    <col min="23" max="23" width="31.42578125" customWidth="1"/>
+    <col min="24" max="24" width="42.7109375" customWidth="1"/>
+    <col min="25" max="25" width="38.42578125" customWidth="1"/>
+    <col min="26" max="26" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -1423,58 +1516,67 @@
         <v>30</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1494,67 +1596,78 @@
         <v>600</v>
       </c>
       <c r="G2">
+        <v>600</v>
+      </c>
+      <c r="H2">
         <v>163</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>50</v>
       </c>
-      <c r="I2">
-        <f>H2*0.05</f>
+      <c r="J2">
+        <f>I2*0.05</f>
         <v>2.5</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>27.4</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1000</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>1E-3</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>521.41999999999996</v>
       </c>
-      <c r="O2" s="5">
+      <c r="P2" s="5">
         <v>0.9</v>
       </c>
-      <c r="P2" s="5">
-        <f t="shared" ref="P2:S7" si="0">$N2*(1+1/$O2)</f>
+      <c r="Q2" s="5">
+        <f t="shared" ref="Q2:U7" si="0">$O2*(1+1/$P2)</f>
         <v>1100.7755555555555</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="R2" s="5">
         <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
-      <c r="R2" s="5">
+      <c r="S2" s="5">
         <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
-      <c r="S2" s="5">
+      <c r="T2" s="5">
         <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
-      <c r="T2" s="6">
-        <f t="shared" ref="T2:T7" si="1">$N2/($O2*$C2)</f>
+      <c r="U2" s="5">
+        <f t="shared" si="0"/>
+        <v>1100.7755555555555</v>
+      </c>
+      <c r="V2" s="6">
+        <f>$O2/($P2*$C2)</f>
         <v>2.084012789768185</v>
       </c>
-      <c r="U2" s="6">
-        <f t="shared" ref="U2:U7" si="2">$N2/($O2*$D2)</f>
+      <c r="W2" s="6">
+        <f>$O2/($P2*$D2)</f>
         <v>1.4130623306233061</v>
       </c>
-      <c r="V2" s="6">
-        <f t="shared" ref="V2:V7" si="3">$N2/($O2*$E2)</f>
+      <c r="X2" s="6">
+        <f>$O2/($P2*$E2)</f>
         <v>1.0728806584362138</v>
       </c>
-      <c r="W2" s="6">
-        <f t="shared" ref="W2:W7" si="4">$N2/($O2*$F2)</f>
+      <c r="Y2" s="6">
+        <f>$O2/($P2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z2" s="6">
+        <f>$O2/($P2*$F2)</f>
+        <v>0.96559259259259256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1574,67 +1687,78 @@
         <v>250</v>
       </c>
       <c r="G3">
+        <v>250</v>
+      </c>
+      <c r="H3">
         <v>299.25</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>175</v>
       </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I7" si="5">H3*0.05</f>
+      <c r="J3">
+        <f t="shared" ref="J3:J7" si="1">I3*0.05</f>
         <v>8.75</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>3.6</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1000</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1E-3</v>
       </c>
-      <c r="N3" s="5">
+      <c r="O3" s="5">
         <v>967.65</v>
       </c>
-      <c r="O3" s="5">
+      <c r="P3" s="5">
         <v>0.9</v>
       </c>
-      <c r="P3" s="5">
+      <c r="Q3" s="5">
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="R3" s="5">
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="R3" s="5">
+      <c r="S3" s="5">
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="S3" s="5">
+      <c r="T3" s="5">
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="T3" s="6">
-        <f t="shared" si="1"/>
+      <c r="U3" s="5">
+        <f t="shared" si="0"/>
+        <v>2042.8166666666666</v>
+      </c>
+      <c r="V3" s="6">
+        <f>$O3/($P3*$C3)</f>
         <v>18.226253037237949</v>
       </c>
-      <c r="U3" s="6">
-        <f t="shared" si="2"/>
+      <c r="W3" s="6">
+        <f>$O3/($P3*$D3)</f>
         <v>15.811274509803921</v>
       </c>
-      <c r="V3" s="6">
-        <f t="shared" si="3"/>
+      <c r="X3" s="6">
+        <f>$O3/($P3*$E3)</f>
         <v>7.4149425287356321</v>
       </c>
-      <c r="W3" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y3" s="6">
+        <f>$O3/($P3*$F3)</f>
         <v>4.3006666666666664</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z3" s="6">
+        <f>$O3/($P3*$F3)</f>
+        <v>4.3006666666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1654,67 +1778,78 @@
         <v>115</v>
       </c>
       <c r="G4">
+        <v>115</v>
+      </c>
+      <c r="H4">
         <v>321.25</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>175</v>
       </c>
-      <c r="I4">
-        <f t="shared" si="5"/>
+      <c r="J4">
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>14.5</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1000</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1E-3</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>561.07000000000005</v>
       </c>
-      <c r="O4" s="5">
+      <c r="P4" s="5">
         <v>0.9</v>
       </c>
-      <c r="P4" s="5">
+      <c r="Q4" s="5">
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="R4" s="5">
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="R4" s="5">
+      <c r="S4" s="5">
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="S4" s="5">
+      <c r="T4" s="5">
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="T4" s="6">
-        <f t="shared" si="1"/>
+      <c r="U4" s="5">
+        <f t="shared" si="0"/>
+        <v>1184.4811111111112</v>
+      </c>
+      <c r="V4" s="6">
+        <f>$O4/($P4*$C4)</f>
         <v>16.289812153412885</v>
       </c>
-      <c r="U4" s="6">
-        <f t="shared" si="2"/>
+      <c r="W4" s="6">
+        <f>$O4/($P4*$D4)</f>
         <v>8.9058730158730164</v>
       </c>
-      <c r="V4" s="6">
-        <f t="shared" si="3"/>
+      <c r="X4" s="6">
+        <f>$O4/($P4*$E4)</f>
         <v>6.5622222222222231</v>
       </c>
-      <c r="W4" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y4" s="6">
+        <f>$O4/($P4*$F4)</f>
         <v>5.4209661835748797</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z4" s="6">
+        <f>$O4/($P4*$F4)</f>
+        <v>5.4209661835748797</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1734,67 +1869,78 @@
         <v>460</v>
       </c>
       <c r="G5">
+        <v>460</v>
+      </c>
+      <c r="H5">
         <v>265.75204563977178</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>57.5</v>
       </c>
-      <c r="I5">
-        <f t="shared" si="5"/>
+      <c r="J5">
+        <f t="shared" si="1"/>
         <v>2.875</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>3.2479999999999989</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1000</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1E-3</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>534.14</v>
       </c>
-      <c r="O5" s="5">
+      <c r="P5" s="5">
         <v>0.9</v>
       </c>
-      <c r="P5" s="5">
+      <c r="Q5" s="5">
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="R5" s="5">
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="R5" s="5">
+      <c r="S5" s="5">
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="S5" s="5">
+      <c r="T5" s="5">
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="T5" s="6">
-        <f t="shared" si="1"/>
+      <c r="U5" s="5">
+        <f t="shared" si="0"/>
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="V5" s="6">
+        <f>$O5/($P5*$C5)</f>
         <v>12.092275649732862</v>
       </c>
-      <c r="U5" s="6">
-        <f t="shared" si="2"/>
+      <c r="W5" s="6">
+        <f>$O5/($P5*$D5)</f>
         <v>2.046513409961686</v>
       </c>
-      <c r="V5" s="6">
-        <f t="shared" si="3"/>
+      <c r="X5" s="6">
+        <f>$O5/($P5*$E5)</f>
         <v>1.5826370370370371</v>
       </c>
-      <c r="W5" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y5" s="6">
+        <f>$O5/($P5*$F5)</f>
         <v>1.2901932367149758</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z5" s="6">
+        <f>$O5/($P5*$F5)</f>
+        <v>1.2901932367149758</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1814,67 +1960,78 @@
         <v>90</v>
       </c>
       <c r="G6">
+        <v>90</v>
+      </c>
+      <c r="H6">
         <v>180.93</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>150</v>
       </c>
-      <c r="I6">
-        <f t="shared" si="5"/>
+      <c r="J6">
+        <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.2</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>1E-3</v>
       </c>
-      <c r="N6" s="5">
+      <c r="O6" s="5">
         <v>1135.5999999999999</v>
       </c>
-      <c r="O6" s="5">
+      <c r="P6" s="5">
         <v>0.9</v>
       </c>
-      <c r="P6" s="5">
+      <c r="Q6" s="5">
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="R6" s="5">
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="R6" s="5">
+      <c r="S6" s="5">
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="S6" s="5">
+      <c r="T6" s="5">
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="T6" s="6">
-        <f t="shared" si="1"/>
+      <c r="U6" s="5">
+        <f t="shared" si="0"/>
+        <v>2397.3777777777777</v>
+      </c>
+      <c r="V6" s="6">
+        <f>$O6/($P6*$C6)</f>
         <v>69.328449328449324</v>
       </c>
-      <c r="U6" s="6">
-        <f t="shared" si="2"/>
+      <c r="W6" s="6">
+        <f>$O6/($P6*$D6)</f>
         <v>38.235690235690235</v>
       </c>
-      <c r="V6" s="6">
-        <f t="shared" si="3"/>
+      <c r="X6" s="6">
+        <f>$O6/($P6*$E6)</f>
         <v>20.351254480286734</v>
       </c>
-      <c r="W6" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y6" s="6">
+        <f>$O6/($P6*$F6)</f>
         <v>14.019753086419753</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Z6" s="6">
+        <f>$O6/($P6*$F6)</f>
+        <v>14.019753086419753</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1894,112 +2051,123 @@
         <v>180</v>
       </c>
       <c r="G7">
+        <v>180</v>
+      </c>
+      <c r="H7">
         <v>353.38</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>125</v>
       </c>
-      <c r="I7">
-        <f t="shared" si="5"/>
+      <c r="J7">
+        <f t="shared" si="1"/>
         <v>6.25</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>8.6799999999999962</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1E-3</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>969.52</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>0.9</v>
       </c>
-      <c r="P7" s="5">
+      <c r="Q7" s="5">
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="R7" s="5">
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="R7" s="5">
+      <c r="S7" s="5">
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="S7" s="5">
+      <c r="T7" s="5">
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="T7" s="6">
-        <f t="shared" si="1"/>
+      <c r="U7" s="5">
+        <f t="shared" si="0"/>
+        <v>2046.7644444444445</v>
+      </c>
+      <c r="V7" s="6">
+        <f>$O7/($P7*$C7)</f>
         <v>39.016459414865786</v>
       </c>
-      <c r="U7" s="6">
-        <f t="shared" si="2"/>
+      <c r="W7" s="6">
+        <f>$O7/($P7*$D7)</f>
         <v>11.895367098547309</v>
       </c>
-      <c r="V7" s="6">
-        <f t="shared" si="3"/>
+      <c r="X7" s="6">
+        <f>$O7/($P7*$E7)</f>
         <v>8.2864957264957262</v>
       </c>
-      <c r="W7" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y7" s="6">
+        <f>$O7/($P7*$F7)</f>
         <v>5.9846913580246914</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="T8" s="4"/>
+      <c r="Z7" s="6">
+        <f>$O7/($P7*$F7)</f>
+        <v>5.9846913580246914</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X8" s="4"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:23" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="24" spans="18:22" x14ac:dyDescent="0.35">
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="18:22" x14ac:dyDescent="0.35">
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="18:22" x14ac:dyDescent="0.35">
-      <c r="R26" s="3"/>
+    <row r="24" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="19:23" x14ac:dyDescent="0.25">
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2011,9 +2179,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -2036,7 +2204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2059,7 +2227,7 @@
         <v>14.59645230960589</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2082,7 +2250,7 @@
         <v>8.4362881656626847</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2105,7 +2273,7 @@
         <v>14.449824965889</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2128,7 +2296,7 @@
         <v>18.882414716557939</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2151,7 +2319,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2182,14 +2350,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09D3F73-E1D3-47E1-9704-FADEA509A785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E25D12-2297-4B62-90BD-0A9C111A788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4305" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$Y$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$X$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{3BD3B233-C8F3-4C4E-A8E9-4D00AB9FAA5A}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{3BD3B233-C8F3-4C4E-A8E9-4D00AB9FAA5A}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -185,7 +185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{2C5B7B49-3F16-4D84-B7A7-EAEBC7F68F01}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{2C5B7B49-3F16-4D84-B7A7-EAEBC7F68F01}">
       <text>
         <r>
           <rPr>
@@ -218,7 +218,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
   <si>
     <t>setting</t>
   </si>
@@ -393,9 +393,6 @@
   </si>
   <si>
     <t>a_dem_2045_usd_per_kw</t>
-  </si>
-  <si>
-    <t>dmax_2045_gw</t>
   </si>
 </sst>
 </file>
@@ -477,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -493,6 +490,7 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -520,7 +518,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -569,7 +567,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -623,7 +621,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -677,7 +675,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -731,7 +729,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -785,7 +783,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -839,7 +837,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -893,7 +891,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -947,7 +945,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -1001,7 +999,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -1055,7 +1053,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1041400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
@@ -1109,7 +1107,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>1371600</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
@@ -1131,6 +1129,168 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="8296275" cy="6353175"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAE2465-B2D2-DB0F-102C-8721179D3A1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8277225" cy="6353175"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5F72BF3-E157-8BBA-5332-8560B201DD62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8277225" cy="6353175"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE5849E7-9615-192A-5AE6-B395D7A5F35D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8277225" cy="6353175"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1466,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1474,29 +1634,28 @@
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="30.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="27.85546875" customWidth="1"/>
-    <col min="17" max="17" width="25.42578125" customWidth="1"/>
-    <col min="18" max="18" width="24.140625" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" customWidth="1"/>
-    <col min="20" max="20" width="28.5703125" customWidth="1"/>
-    <col min="21" max="21" width="34.5703125" customWidth="1"/>
-    <col min="22" max="22" width="31.85546875" customWidth="1"/>
-    <col min="23" max="23" width="31.42578125" customWidth="1"/>
-    <col min="24" max="24" width="42.7109375" customWidth="1"/>
-    <col min="25" max="25" width="38.42578125" customWidth="1"/>
-    <col min="26" max="26" width="36.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="30.5703125" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="27.85546875" customWidth="1"/>
+    <col min="16" max="16" width="25.42578125" customWidth="1"/>
+    <col min="17" max="17" width="24.140625" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" customWidth="1"/>
+    <col min="19" max="19" width="28.5703125" customWidth="1"/>
+    <col min="20" max="20" width="34.5703125" customWidth="1"/>
+    <col min="21" max="21" width="31.85546875" customWidth="1"/>
+    <col min="22" max="22" width="31.42578125" customWidth="1"/>
+    <col min="23" max="23" width="42.7109375" customWidth="1"/>
+    <col min="24" max="24" width="38.42578125" customWidth="1"/>
+    <col min="25" max="25" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -1516,67 +1675,64 @@
         <v>30</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z1" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1596,38 +1752,39 @@
         <v>600</v>
       </c>
       <c r="G2">
-        <v>600</v>
+        <v>163</v>
       </c>
       <c r="H2">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <f>H2*0.05</f>
+        <v>2.5</v>
       </c>
       <c r="J2">
-        <f>I2*0.05</f>
-        <v>2.5</v>
+        <v>27.4</v>
       </c>
       <c r="K2">
-        <v>27.4</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M2">
-        <v>1000</v>
-      </c>
-      <c r="N2">
         <v>1E-3</v>
       </c>
+      <c r="N2" s="5">
+        <v>521.41999999999996</v>
+      </c>
       <c r="O2" s="5">
-        <v>521.41999999999996</v>
+        <v>0.9</v>
       </c>
       <c r="P2" s="5">
-        <v>0.9</v>
+        <f t="shared" ref="P2:T7" si="0">$N2*(1+1/$O2)</f>
+        <v>1100.7755555555555</v>
       </c>
       <c r="Q2" s="5">
-        <f t="shared" ref="Q2:U7" si="0">$O2*(1+1/$P2)</f>
+        <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
       <c r="R2" s="5">
@@ -1642,32 +1799,28 @@
         <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
-      <c r="U2" s="5">
-        <f t="shared" si="0"/>
-        <v>1100.7755555555555</v>
+      <c r="U2" s="6">
+        <f>$N2/($O2*$C2)</f>
+        <v>2.084012789768185</v>
       </c>
       <c r="V2" s="6">
-        <f>$O2/($P2*$C2)</f>
-        <v>2.084012789768185</v>
+        <f>$N2/($O2*$D2)</f>
+        <v>1.4130623306233061</v>
       </c>
       <c r="W2" s="6">
-        <f>$O2/($P2*$D2)</f>
-        <v>1.4130623306233061</v>
+        <f>$N2/($O2*$E2)</f>
+        <v>1.0728806584362138</v>
       </c>
       <c r="X2" s="6">
-        <f>$O2/($P2*$E2)</f>
-        <v>1.0728806584362138</v>
+        <f>$N2/($O2*$F2)</f>
+        <v>0.96559259259259256</v>
       </c>
       <c r="Y2" s="6">
-        <f>$O2/($P2*$F2)</f>
+        <f>$N2/($O2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
-      <c r="Z2" s="6">
-        <f>$O2/($P2*$F2)</f>
-        <v>0.96559259259259256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1687,35 +1840,36 @@
         <v>250</v>
       </c>
       <c r="G3">
-        <v>250</v>
+        <v>299.25</v>
       </c>
       <c r="H3">
-        <v>299.25</v>
+        <v>175</v>
       </c>
       <c r="I3">
-        <v>175</v>
+        <f t="shared" ref="I3:I7" si="1">H3*0.05</f>
+        <v>8.75</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J7" si="1">I3*0.05</f>
-        <v>8.75</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M3">
-        <v>1000</v>
-      </c>
-      <c r="N3">
         <v>1E-3</v>
       </c>
+      <c r="N3" s="5">
+        <v>967.65</v>
+      </c>
       <c r="O3" s="5">
-        <v>967.65</v>
+        <v>0.9</v>
       </c>
       <c r="P3" s="5">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>2042.8166666666666</v>
       </c>
       <c r="Q3" s="5">
         <f t="shared" si="0"/>
@@ -1733,32 +1887,28 @@
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="U3" s="5">
-        <f t="shared" si="0"/>
-        <v>2042.8166666666666</v>
+      <c r="U3" s="6">
+        <f>$N3/($O3*$C3)</f>
+        <v>18.226253037237949</v>
       </c>
       <c r="V3" s="6">
-        <f>$O3/($P3*$C3)</f>
-        <v>18.226253037237949</v>
+        <f>$N3/($O3*$D3)</f>
+        <v>15.811274509803921</v>
       </c>
       <c r="W3" s="6">
-        <f>$O3/($P3*$D3)</f>
-        <v>15.811274509803921</v>
+        <f>$N3/($O3*$E3)</f>
+        <v>7.4149425287356321</v>
       </c>
       <c r="X3" s="6">
-        <f>$O3/($P3*$E3)</f>
-        <v>7.4149425287356321</v>
+        <f>$N3/($O3*$F3)</f>
+        <v>4.3006666666666664</v>
       </c>
       <c r="Y3" s="6">
-        <f>$O3/($P3*$F3)</f>
+        <f>$N3/($O3*$F3)</f>
         <v>4.3006666666666664</v>
       </c>
-      <c r="Z3" s="6">
-        <f>$O3/($P3*$F3)</f>
-        <v>4.3006666666666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1778,35 +1928,36 @@
         <v>115</v>
       </c>
       <c r="G4">
-        <v>115</v>
+        <v>321.25</v>
       </c>
       <c r="H4">
-        <v>321.25</v>
+        <v>175</v>
       </c>
       <c r="I4">
-        <v>175</v>
-      </c>
-      <c r="J4">
         <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
+      <c r="J4">
+        <v>14.5</v>
+      </c>
       <c r="K4">
-        <v>14.5</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M4">
-        <v>1000</v>
-      </c>
-      <c r="N4">
         <v>1E-3</v>
       </c>
+      <c r="N4" s="5">
+        <v>561.07000000000005</v>
+      </c>
       <c r="O4" s="5">
-        <v>561.07000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="P4" s="5">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>1184.4811111111112</v>
       </c>
       <c r="Q4" s="5">
         <f t="shared" si="0"/>
@@ -1824,32 +1975,28 @@
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="U4" s="5">
-        <f t="shared" si="0"/>
-        <v>1184.4811111111112</v>
+      <c r="U4" s="6">
+        <f>$N4/($O4*$C4)</f>
+        <v>16.289812153412885</v>
       </c>
       <c r="V4" s="6">
-        <f>$O4/($P4*$C4)</f>
-        <v>16.289812153412885</v>
+        <f>$N4/($O4*$D4)</f>
+        <v>8.9058730158730164</v>
       </c>
       <c r="W4" s="6">
-        <f>$O4/($P4*$D4)</f>
-        <v>8.9058730158730164</v>
+        <f>$N4/($O4*$E4)</f>
+        <v>6.5622222222222231</v>
       </c>
       <c r="X4" s="6">
-        <f>$O4/($P4*$E4)</f>
-        <v>6.5622222222222231</v>
+        <f>$N4/($O4*$F4)</f>
+        <v>5.4209661835748797</v>
       </c>
       <c r="Y4" s="6">
-        <f>$O4/($P4*$F4)</f>
+        <f>$N4/($O4*$F4)</f>
         <v>5.4209661835748797</v>
       </c>
-      <c r="Z4" s="6">
-        <f>$O4/($P4*$F4)</f>
-        <v>5.4209661835748797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1869,35 +2016,36 @@
         <v>460</v>
       </c>
       <c r="G5">
-        <v>460</v>
+        <v>265.75</v>
       </c>
       <c r="H5">
-        <v>265.75204563977178</v>
+        <v>57.5</v>
       </c>
       <c r="I5">
-        <v>57.5</v>
-      </c>
-      <c r="J5">
         <f t="shared" si="1"/>
         <v>2.875</v>
       </c>
+      <c r="J5">
+        <v>3.2479999999999989</v>
+      </c>
       <c r="K5">
-        <v>3.2479999999999989</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M5">
-        <v>1000</v>
-      </c>
-      <c r="N5">
         <v>1E-3</v>
       </c>
+      <c r="N5" s="5">
+        <v>534.14</v>
+      </c>
       <c r="O5" s="5">
-        <v>534.14</v>
+        <v>0.9</v>
       </c>
       <c r="P5" s="5">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>1127.6288888888889</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" si="0"/>
@@ -1915,32 +2063,28 @@
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="U5" s="5">
-        <f t="shared" si="0"/>
-        <v>1127.6288888888889</v>
+      <c r="U5" s="6">
+        <f>$N5/($O5*$C5)</f>
+        <v>12.092275649732862</v>
       </c>
       <c r="V5" s="6">
-        <f>$O5/($P5*$C5)</f>
-        <v>12.092275649732862</v>
+        <f>$N5/($O5*$D5)</f>
+        <v>2.046513409961686</v>
       </c>
       <c r="W5" s="6">
-        <f>$O5/($P5*$D5)</f>
-        <v>2.046513409961686</v>
+        <f>$N5/($O5*$E5)</f>
+        <v>1.5826370370370371</v>
       </c>
       <c r="X5" s="6">
-        <f>$O5/($P5*$E5)</f>
-        <v>1.5826370370370371</v>
+        <f>$N5/($O5*$F5)</f>
+        <v>1.2901932367149758</v>
       </c>
       <c r="Y5" s="6">
-        <f>$O5/($P5*$F5)</f>
+        <f>$N5/($O5*$F5)</f>
         <v>1.2901932367149758</v>
       </c>
-      <c r="Z5" s="6">
-        <f>$O5/($P5*$F5)</f>
-        <v>1.2901932367149758</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1960,35 +2104,36 @@
         <v>90</v>
       </c>
       <c r="G6">
-        <v>90</v>
+        <v>180.93</v>
       </c>
       <c r="H6">
-        <v>180.93</v>
+        <v>150</v>
       </c>
       <c r="I6">
-        <v>150</v>
-      </c>
-      <c r="J6">
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M6">
-        <v>1000</v>
-      </c>
-      <c r="N6">
         <v>1E-3</v>
       </c>
+      <c r="N6" s="5">
+        <v>1135.5999999999999</v>
+      </c>
       <c r="O6" s="5">
-        <v>1135.5999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="P6" s="5">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>2397.3777777777777</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
@@ -2006,32 +2151,28 @@
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="U6" s="5">
-        <f t="shared" si="0"/>
-        <v>2397.3777777777777</v>
+      <c r="U6" s="6">
+        <f>$N6/($O6*$C6)</f>
+        <v>69.328449328449324</v>
       </c>
       <c r="V6" s="6">
-        <f>$O6/($P6*$C6)</f>
-        <v>69.328449328449324</v>
+        <f>$N6/($O6*$D6)</f>
+        <v>38.235690235690235</v>
       </c>
       <c r="W6" s="6">
-        <f>$O6/($P6*$D6)</f>
-        <v>38.235690235690235</v>
+        <f>$N6/($O6*$E6)</f>
+        <v>20.351254480286734</v>
       </c>
       <c r="X6" s="6">
-        <f>$O6/($P6*$E6)</f>
-        <v>20.351254480286734</v>
+        <f>$N6/($O6*$F6)</f>
+        <v>14.019753086419753</v>
       </c>
       <c r="Y6" s="6">
-        <f>$O6/($P6*$F6)</f>
+        <f>$N6/($O6*$F6)</f>
         <v>14.019753086419753</v>
       </c>
-      <c r="Z6" s="6">
-        <f>$O6/($P6*$F6)</f>
-        <v>14.019753086419753</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2051,35 +2192,36 @@
         <v>180</v>
       </c>
       <c r="G7">
-        <v>180</v>
+        <v>353.38</v>
       </c>
       <c r="H7">
-        <v>353.38</v>
+        <v>125</v>
       </c>
       <c r="I7">
-        <v>125</v>
-      </c>
-      <c r="J7">
         <f t="shared" si="1"/>
         <v>6.25</v>
       </c>
+      <c r="J7">
+        <v>8.6799999999999962</v>
+      </c>
       <c r="K7">
-        <v>8.6799999999999962</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M7">
-        <v>1000</v>
-      </c>
-      <c r="N7">
         <v>1E-3</v>
       </c>
+      <c r="N7" s="5">
+        <v>969.52</v>
+      </c>
       <c r="O7" s="5">
-        <v>969.52</v>
+        <v>0.9</v>
       </c>
       <c r="P7" s="5">
-        <v>0.9</v>
+        <f t="shared" si="0"/>
+        <v>2046.7644444444445</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
@@ -2097,77 +2239,75 @@
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="U7" s="5">
-        <f t="shared" si="0"/>
-        <v>2046.7644444444445</v>
+      <c r="U7" s="6">
+        <f>$N7/($O7*$C7)</f>
+        <v>39.016459414865786</v>
       </c>
       <c r="V7" s="6">
-        <f>$O7/($P7*$C7)</f>
-        <v>39.016459414865786</v>
+        <f>$N7/($O7*$D7)</f>
+        <v>11.895367098547309</v>
       </c>
       <c r="W7" s="6">
-        <f>$O7/($P7*$D7)</f>
-        <v>11.895367098547309</v>
+        <f>$N7/($O7*$E7)</f>
+        <v>8.2864957264957262</v>
       </c>
       <c r="X7" s="6">
-        <f>$O7/($P7*$E7)</f>
-        <v>8.2864957264957262</v>
+        <f>$N7/($O7*$F7)</f>
+        <v>5.9846913580246914</v>
       </c>
       <c r="Y7" s="6">
-        <f>$O7/($P7*$F7)</f>
+        <f>$N7/($O7*$F7)</f>
         <v>5.9846913580246914</v>
       </c>
-      <c r="Z7" s="6">
-        <f>$O7/($P7*$F7)</f>
-        <v>5.9846913580246914</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="24" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="19:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="18:22" x14ac:dyDescent="0.25">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="18:22" x14ac:dyDescent="0.25">
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="18:22" x14ac:dyDescent="0.25">
+      <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E25D12-2297-4B62-90BD-0A9C111A788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059B2620-8574-4565-BC7A-B393EC739C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4305" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$X$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$W$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -129,21 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{3BD3B233-C8F3-4C4E-A8E9-4D00AB9FAA5A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -185,21 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand slope b_dem_2040 = p_full/(eps_abs_base*dmax_2040). Unit: (USD/kW)/GW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{2C5B7B49-3F16-4D84-B7A7-EAEBC7F68F01}">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -218,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>setting</t>
   </si>
@@ -387,12 +359,6 @@
   </si>
   <si>
     <t>g_exp_ub_per_yr_gw</t>
-  </si>
-  <si>
-    <t>b_dem_2045_usd_per_kw_per_gw</t>
-  </si>
-  <si>
-    <t>a_dem_2045_usd_per_kw</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1647,15 +1613,13 @@
     <col min="17" max="17" width="24.140625" customWidth="1"/>
     <col min="18" max="18" width="22.85546875" customWidth="1"/>
     <col min="19" max="19" width="28.5703125" customWidth="1"/>
-    <col min="20" max="20" width="34.5703125" customWidth="1"/>
-    <col min="21" max="21" width="31.85546875" customWidth="1"/>
-    <col min="22" max="22" width="31.42578125" customWidth="1"/>
-    <col min="23" max="23" width="42.7109375" customWidth="1"/>
-    <col min="24" max="24" width="38.42578125" customWidth="1"/>
-    <col min="25" max="25" width="36.7109375" customWidth="1"/>
+    <col min="20" max="20" width="31.85546875" customWidth="1"/>
+    <col min="21" max="21" width="31.42578125" customWidth="1"/>
+    <col min="22" max="22" width="42.7109375" customWidth="1"/>
+    <col min="23" max="23" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -1714,25 +1678,19 @@
         <v>41</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1780,7 +1738,7 @@
         <v>0.9</v>
       </c>
       <c r="P2" s="5">
-        <f t="shared" ref="P2:T7" si="0">$N2*(1+1/$O2)</f>
+        <f t="shared" ref="P2:S7" si="0">$N2*(1+1/$O2)</f>
         <v>1100.7755555555555</v>
       </c>
       <c r="Q2" s="5">
@@ -1795,32 +1753,24 @@
         <f t="shared" si="0"/>
         <v>1100.7755555555555</v>
       </c>
-      <c r="T2" s="5">
-        <f t="shared" si="0"/>
-        <v>1100.7755555555555</v>
-      </c>
-      <c r="U2" s="6">
+      <c r="T2" s="6">
         <f>$N2/($O2*$C2)</f>
         <v>2.084012789768185</v>
       </c>
-      <c r="V2" s="6">
+      <c r="U2" s="6">
         <f>$N2/($O2*$D2)</f>
         <v>1.4130623306233061</v>
       </c>
-      <c r="W2" s="6">
+      <c r="V2" s="6">
         <f>$N2/($O2*$E2)</f>
         <v>1.0728806584362138</v>
       </c>
-      <c r="X2" s="6">
+      <c r="W2" s="6">
         <f>$N2/($O2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
-      <c r="Y2" s="6">
-        <f>$N2/($O2*$F2)</f>
-        <v>0.96559259259259256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1883,32 +1833,24 @@
         <f t="shared" si="0"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="T3" s="5">
-        <f t="shared" si="0"/>
-        <v>2042.8166666666666</v>
-      </c>
-      <c r="U3" s="6">
+      <c r="T3" s="6">
         <f>$N3/($O3*$C3)</f>
         <v>18.226253037237949</v>
       </c>
-      <c r="V3" s="6">
+      <c r="U3" s="6">
         <f>$N3/($O3*$D3)</f>
         <v>15.811274509803921</v>
       </c>
-      <c r="W3" s="6">
+      <c r="V3" s="6">
         <f>$N3/($O3*$E3)</f>
         <v>7.4149425287356321</v>
       </c>
-      <c r="X3" s="6">
+      <c r="W3" s="6">
         <f>$N3/($O3*$F3)</f>
         <v>4.3006666666666664</v>
       </c>
-      <c r="Y3" s="6">
-        <f>$N3/($O3*$F3)</f>
-        <v>4.3006666666666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1971,32 +1913,24 @@
         <f t="shared" si="0"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="T4" s="5">
-        <f t="shared" si="0"/>
-        <v>1184.4811111111112</v>
-      </c>
-      <c r="U4" s="6">
+      <c r="T4" s="6">
         <f>$N4/($O4*$C4)</f>
         <v>16.289812153412885</v>
       </c>
-      <c r="V4" s="6">
+      <c r="U4" s="6">
         <f>$N4/($O4*$D4)</f>
         <v>8.9058730158730164</v>
       </c>
-      <c r="W4" s="6">
+      <c r="V4" s="6">
         <f>$N4/($O4*$E4)</f>
         <v>6.5622222222222231</v>
       </c>
-      <c r="X4" s="6">
+      <c r="W4" s="6">
         <f>$N4/($O4*$F4)</f>
         <v>5.4209661835748797</v>
       </c>
-      <c r="Y4" s="6">
-        <f>$N4/($O4*$F4)</f>
-        <v>5.4209661835748797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2059,32 +1993,24 @@
         <f t="shared" si="0"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="T5" s="5">
-        <f t="shared" si="0"/>
-        <v>1127.6288888888889</v>
-      </c>
-      <c r="U5" s="6">
+      <c r="T5" s="6">
         <f>$N5/($O5*$C5)</f>
         <v>12.092275649732862</v>
       </c>
-      <c r="V5" s="6">
+      <c r="U5" s="6">
         <f>$N5/($O5*$D5)</f>
         <v>2.046513409961686</v>
       </c>
-      <c r="W5" s="6">
+      <c r="V5" s="6">
         <f>$N5/($O5*$E5)</f>
         <v>1.5826370370370371</v>
       </c>
-      <c r="X5" s="6">
+      <c r="W5" s="6">
         <f>$N5/($O5*$F5)</f>
         <v>1.2901932367149758</v>
       </c>
-      <c r="Y5" s="6">
-        <f>$N5/($O5*$F5)</f>
-        <v>1.2901932367149758</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2147,32 +2073,24 @@
         <f t="shared" si="0"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="T6" s="5">
-        <f t="shared" si="0"/>
-        <v>2397.3777777777777</v>
-      </c>
-      <c r="U6" s="6">
+      <c r="T6" s="6">
         <f>$N6/($O6*$C6)</f>
         <v>69.328449328449324</v>
       </c>
-      <c r="V6" s="6">
+      <c r="U6" s="6">
         <f>$N6/($O6*$D6)</f>
         <v>38.235690235690235</v>
       </c>
-      <c r="W6" s="6">
+      <c r="V6" s="6">
         <f>$N6/($O6*$E6)</f>
         <v>20.351254480286734</v>
       </c>
-      <c r="X6" s="6">
+      <c r="W6" s="6">
         <f>$N6/($O6*$F6)</f>
         <v>14.019753086419753</v>
       </c>
-      <c r="Y6" s="6">
-        <f>$N6/($O6*$F6)</f>
-        <v>14.019753086419753</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2235,79 +2153,69 @@
         <f t="shared" si="0"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="T7" s="5">
-        <f t="shared" si="0"/>
-        <v>2046.7644444444445</v>
-      </c>
-      <c r="U7" s="6">
+      <c r="T7" s="6">
         <f>$N7/($O7*$C7)</f>
         <v>39.016459414865786</v>
       </c>
-      <c r="V7" s="6">
+      <c r="U7" s="6">
         <f>$N7/($O7*$D7)</f>
         <v>11.895367098547309</v>
       </c>
-      <c r="W7" s="6">
+      <c r="V7" s="6">
         <f>$N7/($O7*$E7)</f>
         <v>8.2864957264957262</v>
       </c>
-      <c r="X7" s="6">
+      <c r="W7" s="6">
         <f>$N7/($O7*$F7)</f>
         <v>5.9846913580246914</v>
       </c>
-      <c r="Y7" s="6">
-        <f>$N7/($O7*$F7)</f>
-        <v>5.9846913580246914</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
     </row>
-    <row r="24" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="18:21" x14ac:dyDescent="0.25">
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="18:21" x14ac:dyDescent="0.25">
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="18:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="18:21" x14ac:dyDescent="0.25">
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059B2620-8574-4565-BC7A-B393EC739C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA6795-544C-489D-8F5D-A4E10F368C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4305" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="params_region" sheetId="3" r:id="rId3"/>
     <sheet name="c_ship" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
+    <sheet name="Tabelle1" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$W$7</definedName>
@@ -1281,6 +1282,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8411C01E-62C1-ADD4-8278-1034838A370D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8353425" cy="6353175"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D27578-1DDD-A5D9-A322-1D8339A3936C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8353425" cy="6353175"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1754,19 +1863,19 @@
         <v>1100.7755555555555</v>
       </c>
       <c r="T2" s="6">
-        <f>$N2/($O2*$C2)</f>
+        <f t="shared" ref="T2:T7" si="1">$N2/($O2*$C2)</f>
         <v>2.084012789768185</v>
       </c>
       <c r="U2" s="6">
-        <f>$N2/($O2*$D2)</f>
+        <f t="shared" ref="U2:U7" si="2">$N2/($O2*$D2)</f>
         <v>1.4130623306233061</v>
       </c>
       <c r="V2" s="6">
-        <f>$N2/($O2*$E2)</f>
+        <f t="shared" ref="V2:V7" si="3">$N2/($O2*$E2)</f>
         <v>1.0728806584362138</v>
       </c>
       <c r="W2" s="6">
-        <f>$N2/($O2*$F2)</f>
+        <f t="shared" ref="W2:W7" si="4">$N2/($O2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
     </row>
@@ -1796,7 +1905,7 @@
         <v>175</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I7" si="1">H3*0.05</f>
+        <f t="shared" ref="I3:I7" si="5">H3*0.05</f>
         <v>8.75</v>
       </c>
       <c r="J3">
@@ -1834,19 +1943,19 @@
         <v>2042.8166666666666</v>
       </c>
       <c r="T3" s="6">
-        <f>$N3/($O3*$C3)</f>
+        <f t="shared" si="1"/>
         <v>18.226253037237949</v>
       </c>
       <c r="U3" s="6">
-        <f>$N3/($O3*$D3)</f>
+        <f t="shared" si="2"/>
         <v>15.811274509803921</v>
       </c>
       <c r="V3" s="6">
-        <f>$N3/($O3*$E3)</f>
+        <f t="shared" si="3"/>
         <v>7.4149425287356321</v>
       </c>
       <c r="W3" s="6">
-        <f>$N3/($O3*$F3)</f>
+        <f t="shared" si="4"/>
         <v>4.3006666666666664</v>
       </c>
     </row>
@@ -1876,7 +1985,7 @@
         <v>175</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
       <c r="J4">
@@ -1914,19 +2023,19 @@
         <v>1184.4811111111112</v>
       </c>
       <c r="T4" s="6">
-        <f>$N4/($O4*$C4)</f>
+        <f t="shared" si="1"/>
         <v>16.289812153412885</v>
       </c>
       <c r="U4" s="6">
-        <f>$N4/($O4*$D4)</f>
+        <f t="shared" si="2"/>
         <v>8.9058730158730164</v>
       </c>
       <c r="V4" s="6">
-        <f>$N4/($O4*$E4)</f>
+        <f t="shared" si="3"/>
         <v>6.5622222222222231</v>
       </c>
       <c r="W4" s="6">
-        <f>$N4/($O4*$F4)</f>
+        <f t="shared" si="4"/>
         <v>5.4209661835748797</v>
       </c>
     </row>
@@ -1956,7 +2065,7 @@
         <v>57.5</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.875</v>
       </c>
       <c r="J5">
@@ -1994,19 +2103,19 @@
         <v>1127.6288888888889</v>
       </c>
       <c r="T5" s="6">
-        <f>$N5/($O5*$C5)</f>
+        <f t="shared" si="1"/>
         <v>12.092275649732862</v>
       </c>
       <c r="U5" s="6">
-        <f>$N5/($O5*$D5)</f>
+        <f t="shared" si="2"/>
         <v>2.046513409961686</v>
       </c>
       <c r="V5" s="6">
-        <f>$N5/($O5*$E5)</f>
+        <f t="shared" si="3"/>
         <v>1.5826370370370371</v>
       </c>
       <c r="W5" s="6">
-        <f>$N5/($O5*$F5)</f>
+        <f t="shared" si="4"/>
         <v>1.2901932367149758</v>
       </c>
     </row>
@@ -2036,7 +2145,7 @@
         <v>150</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7.5</v>
       </c>
       <c r="J6">
@@ -2074,19 +2183,19 @@
         <v>2397.3777777777777</v>
       </c>
       <c r="T6" s="6">
-        <f>$N6/($O6*$C6)</f>
+        <f t="shared" si="1"/>
         <v>69.328449328449324</v>
       </c>
       <c r="U6" s="6">
-        <f>$N6/($O6*$D6)</f>
+        <f t="shared" si="2"/>
         <v>38.235690235690235</v>
       </c>
       <c r="V6" s="6">
-        <f>$N6/($O6*$E6)</f>
+        <f t="shared" si="3"/>
         <v>20.351254480286734</v>
       </c>
       <c r="W6" s="6">
-        <f>$N6/($O6*$F6)</f>
+        <f t="shared" si="4"/>
         <v>14.019753086419753</v>
       </c>
     </row>
@@ -2116,7 +2225,7 @@
         <v>125</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.25</v>
       </c>
       <c r="J7">
@@ -2154,19 +2263,19 @@
         <v>2046.7644444444445</v>
       </c>
       <c r="T7" s="6">
-        <f>$N7/($O7*$C7)</f>
+        <f t="shared" si="1"/>
         <v>39.016459414865786</v>
       </c>
       <c r="U7" s="6">
-        <f>$N7/($O7*$D7)</f>
+        <f t="shared" si="2"/>
         <v>11.895367098547309</v>
       </c>
       <c r="V7" s="6">
-        <f>$N7/($O7*$E7)</f>
+        <f t="shared" si="3"/>
         <v>8.2864957264957262</v>
       </c>
       <c r="W7" s="6">
-        <f>$N7/($O7*$F7)</f>
+        <f t="shared" si="4"/>
         <v>5.9846913580246914</v>
       </c>
     </row>
@@ -2413,4 +2522,44 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65F6B1E-E1AD-4789-BB0A-188C512086A4}">
+  <dimension ref="C8:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>3.2479999999999989</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>8.6799999999999962</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA6795-544C-489D-8F5D-A4E10F368C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B907D735-A300-49B9-83F4-46BAB72A5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4095" yWindow="3285" windowWidth="31530" windowHeight="16905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,8 @@
     <sheet name="c_ship" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
     <sheet name="Tabelle1" sheetId="6" r:id="rId6"/>
+    <sheet name="initial_state" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_region!$A$1:$W$7</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -191,7 +189,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>qcap_exist_gw</t>
+  </si>
+  <si>
+    <t>dmax_2025_gw</t>
+  </si>
+  <si>
+    <t>dmax_2030_gw</t>
+  </si>
+  <si>
+    <t>dmax_2035_gw</t>
+  </si>
+  <si>
+    <t>dmax_2040_gw</t>
+  </si>
+  <si>
+    <t>c_man_usd_per_kw</t>
+  </si>
+  <si>
+    <t>c_inv_musd_per_gw_per_yr</t>
+  </si>
+  <si>
+    <t>c_hold_musd_per_gw_per_yr</t>
+  </si>
+  <si>
+    <t>g_exp_ub_per_yr_gw</t>
+  </si>
+  <si>
+    <t>g_dec_ub_per_yr</t>
+  </si>
+  <si>
+    <t>p_offer_max_usd_per_kw</t>
+  </si>
+  <si>
+    <t>rho_p_scalar</t>
+  </si>
+  <si>
+    <t>p_full_usd_per_kw</t>
+  </si>
+  <si>
+    <t>eps_abs_base_scalar</t>
+  </si>
+  <si>
+    <t>a_dem_2025_usd_per_kw</t>
+  </si>
+  <si>
+    <t>a_dem_2030_usd_per_kw</t>
+  </si>
+  <si>
+    <t>a_dem_2035_usd_per_kw</t>
+  </si>
+  <si>
+    <t>a_dem_2040_usd_per_kw</t>
+  </si>
+  <si>
+    <t>b_dem_2025_usd_per_kw_per_gw</t>
+  </si>
+  <si>
+    <t>b_dem_2030_usd_per_kw_per_gw</t>
+  </si>
+  <si>
+    <t>b_dem_2035_usd_per_kw_per_gw</t>
+  </si>
+  <si>
+    <t>b_dem_2040_usd_per_kw_per_gw</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>eu</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>roa</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
   <si>
     <t>setting</t>
   </si>
@@ -229,27 +314,15 @@
     <t>scenario_capitalistic_china</t>
   </si>
   <si>
-    <t>region</t>
-  </si>
-  <si>
     <t>region_name</t>
   </si>
   <si>
-    <t>ch</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
-    <t>eu</t>
-  </si>
-  <si>
     <t>Europe</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>North America</t>
   </si>
   <si>
@@ -259,76 +332,10 @@
     <t>Asia (APAC+ROA)</t>
   </si>
   <si>
-    <t>af</t>
-  </si>
-  <si>
     <t>Africa</t>
   </si>
   <si>
-    <t>row</t>
-  </si>
-  <si>
     <t>Rest of World</t>
-  </si>
-  <si>
-    <t>qcap_exist_gw</t>
-  </si>
-  <si>
-    <t>dmax_2025_gw</t>
-  </si>
-  <si>
-    <t>dmax_2030_gw</t>
-  </si>
-  <si>
-    <t>dmax_2035_gw</t>
-  </si>
-  <si>
-    <t>dmax_2040_gw</t>
-  </si>
-  <si>
-    <t>c_man_usd_per_kw</t>
-  </si>
-  <si>
-    <t>c_inv_musd_per_gw_per_yr</t>
-  </si>
-  <si>
-    <t>g_dec_ub_per_yr</t>
-  </si>
-  <si>
-    <t>p_offer_max_usd_per_kw</t>
-  </si>
-  <si>
-    <t>rho_p_scalar</t>
-  </si>
-  <si>
-    <t>p_full_usd_per_kw</t>
-  </si>
-  <si>
-    <t>eps_abs_base_scalar</t>
-  </si>
-  <si>
-    <t>a_dem_2025_usd_per_kw</t>
-  </si>
-  <si>
-    <t>a_dem_2030_usd_per_kw</t>
-  </si>
-  <si>
-    <t>a_dem_2035_usd_per_kw</t>
-  </si>
-  <si>
-    <t>a_dem_2040_usd_per_kw</t>
-  </si>
-  <si>
-    <t>b_dem_2025_usd_per_kw_per_gw</t>
-  </si>
-  <si>
-    <t>b_dem_2030_usd_per_kw_per_gw</t>
-  </si>
-  <si>
-    <t>b_dem_2035_usd_per_kw_per_gw</t>
-  </si>
-  <si>
-    <t>b_dem_2040_usd_per_kw_per_gw</t>
   </si>
   <si>
     <t>exporter</t>
@@ -353,13 +360,49 @@
 </t>
   </si>
   <si>
-    <t>c_hold_musd_per_gw_per_yr</t>
-  </si>
-  <si>
-    <t>roa</t>
-  </si>
-  <si>
-    <t>g_exp_ub_per_yr_gw</t>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Q_offer</t>
+  </si>
+  <si>
+    <t>dK_net</t>
+  </si>
+  <si>
+    <t>a_bid</t>
+  </si>
+  <si>
+    <t>p_offer_ch</t>
+  </si>
+  <si>
+    <t>p_offer_eu</t>
+  </si>
+  <si>
+    <t>p_offer_us</t>
+  </si>
+  <si>
+    <t>p_offer_apac</t>
+  </si>
+  <si>
+    <t>p_offer_af</t>
+  </si>
+  <si>
+    <t>p_offer_row</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>2035</t>
+  </si>
+  <si>
+    <t>2040</t>
+  </si>
+  <si>
+    <t>2045</t>
   </si>
 </sst>
 </file>
@@ -369,7 +412,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +433,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -399,7 +447,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -437,11 +485,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -458,6 +521,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -473,924 +539,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1035" name="Text Box 11" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA58BB55-35A2-9187-2F9E-435D0532AB7C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="6350000" cy="6350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20DB40AD-A801-AFC5-29B1-3FEB6B1D978B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15032E20-A5F3-B083-8014-3334C15DB993}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F950EA5-5C9E-07B9-A431-6203687B16CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF077932-AB85-5284-F139-1A17DAC5BD2C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A28031-2919-2EBA-1038-0AB0ED981ED7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AFB1342-4107-852A-346B-EF7E40FB286A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3361DFC-9C6A-3512-24A2-CB9D19AE59B1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9610934A-61E7-AFCD-A513-99981C840CF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{602025C5-2E30-3980-7139-BCA302E673FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E08AE79-14AE-B6A1-136A-B86C4FF1DC6A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8299450" cy="6350000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F95148C-FA07-E8BD-33E4-E4A856624368}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8296275" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAE2465-B2D2-DB0F-102C-8721179D3A1F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8277225" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5F72BF3-E157-8BBA-5332-8560B201DD62}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8277225" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE5849E7-9615-192A-5AE6-B395D7A5F35D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8277225" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8411C01E-62C1-ADD4-8278-1034838A370D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8353425" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D27578-1DDD-A5D9-A322-1D8339A3936C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8353425" cy="6353175"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst/>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1574,58 +722,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1640,58 +788,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1730,78 +878,78 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>931</v>
@@ -1825,7 +973,7 @@
         <v>50</v>
       </c>
       <c r="I2">
-        <f>H2*0.05</f>
+        <f t="shared" ref="I2:I7" si="0">H2*0.05</f>
         <v>2.5</v>
       </c>
       <c r="J2">
@@ -1847,41 +995,41 @@
         <v>0.9</v>
       </c>
       <c r="P2" s="5">
-        <f t="shared" ref="P2:S7" si="0">$N2*(1+1/$O2)</f>
+        <f t="shared" ref="P2:S7" si="1">$N2*(1+1/$O2)</f>
         <v>1100.7755555555555</v>
       </c>
       <c r="Q2" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1100.7755555555555</v>
       </c>
       <c r="R2" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1100.7755555555555</v>
       </c>
       <c r="S2" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1100.7755555555555</v>
       </c>
       <c r="T2" s="6">
-        <f t="shared" ref="T2:T7" si="1">$N2/($O2*$C2)</f>
+        <f t="shared" ref="T2:T7" si="2">$N2/($O2*$C2)</f>
         <v>2.084012789768185</v>
       </c>
       <c r="U2" s="6">
-        <f t="shared" ref="U2:U7" si="2">$N2/($O2*$D2)</f>
+        <f t="shared" ref="U2:U7" si="3">$N2/($O2*$D2)</f>
         <v>1.4130623306233061</v>
       </c>
       <c r="V2" s="6">
-        <f t="shared" ref="V2:V7" si="3">$N2/($O2*$E2)</f>
+        <f t="shared" ref="V2:V7" si="4">$N2/($O2*$E2)</f>
         <v>1.0728806584362138</v>
       </c>
       <c r="W2" s="6">
-        <f t="shared" ref="W2:W7" si="4">$N2/($O2*$F2)</f>
+        <f t="shared" ref="W2:W7" si="5">$N2/($O2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>22</v>
@@ -1905,7 +1053,7 @@
         <v>175</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I7" si="5">H3*0.05</f>
+        <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
       <c r="J3">
@@ -1927,41 +1075,41 @@
         <v>0.9</v>
       </c>
       <c r="P3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
       <c r="Q3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
       <c r="R3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
       <c r="S3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
       <c r="T3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18.226253037237949</v>
       </c>
       <c r="U3" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15.811274509803921</v>
       </c>
       <c r="V3" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.4149425287356321</v>
       </c>
       <c r="W3" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.3006666666666664</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>42</v>
@@ -1985,7 +1133,7 @@
         <v>175</v>
       </c>
       <c r="I4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
       <c r="J4">
@@ -2007,41 +1155,41 @@
         <v>0.9</v>
       </c>
       <c r="P4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
       <c r="Q4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
       <c r="R4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
       <c r="S4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
       <c r="T4" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.289812153412885</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.9058730158730164</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.5622222222222231</v>
       </c>
       <c r="W4" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.4209661835748797</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>110</v>
@@ -2065,7 +1213,7 @@
         <v>57.5</v>
       </c>
       <c r="I5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>2.875</v>
       </c>
       <c r="J5">
@@ -2087,41 +1235,41 @@
         <v>0.9</v>
       </c>
       <c r="P5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
       <c r="Q5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
       <c r="R5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
       <c r="S5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.092275649732862</v>
       </c>
       <c r="U5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.046513409961686</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5826370370370371</v>
       </c>
       <c r="W5" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2901932367149758</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>3.4</v>
@@ -2145,7 +1293,7 @@
         <v>150</v>
       </c>
       <c r="I6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="J6">
@@ -2167,41 +1315,41 @@
         <v>0.9</v>
       </c>
       <c r="P6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
       <c r="Q6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
       <c r="R6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
       <c r="S6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69.328449328449324</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38.235690235690235</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.351254480286734</v>
       </c>
       <c r="W6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14.019753086419753</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>293</v>
@@ -2225,7 +1373,7 @@
         <v>125</v>
       </c>
       <c r="I7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
       <c r="J7">
@@ -2247,35 +1395,35 @@
         <v>0.9</v>
       </c>
       <c r="P7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
       <c r="Q7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
       <c r="R7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
       <c r="S7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
       <c r="T7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39.016459414865786</v>
       </c>
       <c r="U7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.895367098547309</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.2864957264957262</v>
       </c>
       <c r="W7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.9846913580246914</v>
       </c>
     </row>
@@ -2328,8 +1476,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2340,30 +1487,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2386,7 +1533,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>16.117999999999999</v>
@@ -2409,7 +1556,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>24.731000000000002</v>
@@ -2432,7 +1579,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>13.232892950285249</v>
@@ -2455,7 +1602,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>4.5</v>
@@ -2478,7 +1625,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>14.122395904436861</v>
@@ -2511,12 +1658,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +1672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65F6B1E-E1AD-4789-BB0A-188C512086A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="C8:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2562,4 +1709,1110 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="31.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>931</v>
+      </c>
+      <c r="D2">
+        <v>27.4</v>
+      </c>
+      <c r="E2">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F2">
+        <v>163</v>
+      </c>
+      <c r="G2">
+        <v>163</v>
+      </c>
+      <c r="H2">
+        <v>163</v>
+      </c>
+      <c r="I2">
+        <v>163</v>
+      </c>
+      <c r="J2">
+        <v>163</v>
+      </c>
+      <c r="K2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>3.6</v>
+      </c>
+      <c r="E3">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F3">
+        <v>299.25</v>
+      </c>
+      <c r="G3">
+        <v>299.25</v>
+      </c>
+      <c r="H3">
+        <v>299.25</v>
+      </c>
+      <c r="I3">
+        <v>299.25</v>
+      </c>
+      <c r="J3">
+        <v>299.25</v>
+      </c>
+      <c r="K3">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>14.5</v>
+      </c>
+      <c r="E4">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F4">
+        <v>321.25</v>
+      </c>
+      <c r="G4">
+        <v>321.25</v>
+      </c>
+      <c r="H4">
+        <v>321.25</v>
+      </c>
+      <c r="I4">
+        <v>321.25</v>
+      </c>
+      <c r="J4">
+        <v>321.25</v>
+      </c>
+      <c r="K4">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>3.2479999999999989</v>
+      </c>
+      <c r="E5">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F5">
+        <v>265.75</v>
+      </c>
+      <c r="G5">
+        <v>265.75</v>
+      </c>
+      <c r="H5">
+        <v>265.75</v>
+      </c>
+      <c r="I5">
+        <v>265.75</v>
+      </c>
+      <c r="J5">
+        <v>265.75</v>
+      </c>
+      <c r="K5">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>3.4</v>
+      </c>
+      <c r="D6">
+        <v>0.2</v>
+      </c>
+      <c r="E6">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F6">
+        <v>180.93</v>
+      </c>
+      <c r="G6">
+        <v>180.93</v>
+      </c>
+      <c r="H6">
+        <v>180.93</v>
+      </c>
+      <c r="I6">
+        <v>180.93</v>
+      </c>
+      <c r="J6">
+        <v>180.93</v>
+      </c>
+      <c r="K6">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>293</v>
+      </c>
+      <c r="D7">
+        <v>8.6799999999999962</v>
+      </c>
+      <c r="E7">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F7">
+        <v>353.38</v>
+      </c>
+      <c r="G7">
+        <v>353.38</v>
+      </c>
+      <c r="H7">
+        <v>353.38</v>
+      </c>
+      <c r="I7">
+        <v>353.38</v>
+      </c>
+      <c r="J7">
+        <v>353.38</v>
+      </c>
+      <c r="K7">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8">
+        <v>1068</v>
+      </c>
+      <c r="D8">
+        <v>27.4</v>
+      </c>
+      <c r="E8">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F8">
+        <v>163</v>
+      </c>
+      <c r="G8">
+        <v>163</v>
+      </c>
+      <c r="H8">
+        <v>163</v>
+      </c>
+      <c r="I8">
+        <v>163</v>
+      </c>
+      <c r="J8">
+        <v>163</v>
+      </c>
+      <c r="K8">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>3.6</v>
+      </c>
+      <c r="E9">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F9">
+        <v>299.25</v>
+      </c>
+      <c r="G9">
+        <v>299.25</v>
+      </c>
+      <c r="H9">
+        <v>299.25</v>
+      </c>
+      <c r="I9">
+        <v>299.25</v>
+      </c>
+      <c r="J9">
+        <v>299.25</v>
+      </c>
+      <c r="K9">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10">
+        <v>114.5</v>
+      </c>
+      <c r="D10">
+        <v>14.5</v>
+      </c>
+      <c r="E10">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F10">
+        <v>321.25</v>
+      </c>
+      <c r="G10">
+        <v>321.25</v>
+      </c>
+      <c r="H10">
+        <v>321.25</v>
+      </c>
+      <c r="I10">
+        <v>321.25</v>
+      </c>
+      <c r="J10">
+        <v>321.25</v>
+      </c>
+      <c r="K10">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <v>126.24</v>
+      </c>
+      <c r="D11">
+        <v>3.2479999999999989</v>
+      </c>
+      <c r="E11">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F11">
+        <v>265.75</v>
+      </c>
+      <c r="G11">
+        <v>265.75</v>
+      </c>
+      <c r="H11">
+        <v>265.75</v>
+      </c>
+      <c r="I11">
+        <v>265.75</v>
+      </c>
+      <c r="J11">
+        <v>265.75</v>
+      </c>
+      <c r="K11">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D12">
+        <v>0.2</v>
+      </c>
+      <c r="E12">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F12">
+        <v>180.93</v>
+      </c>
+      <c r="G12">
+        <v>180.93</v>
+      </c>
+      <c r="H12">
+        <v>180.93</v>
+      </c>
+      <c r="I12">
+        <v>180.93</v>
+      </c>
+      <c r="J12">
+        <v>180.93</v>
+      </c>
+      <c r="K12">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13">
+        <v>336.4</v>
+      </c>
+      <c r="D13">
+        <v>8.6799999999999962</v>
+      </c>
+      <c r="E13">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F13">
+        <v>353.38</v>
+      </c>
+      <c r="G13">
+        <v>353.38</v>
+      </c>
+      <c r="H13">
+        <v>353.38</v>
+      </c>
+      <c r="I13">
+        <v>353.38</v>
+      </c>
+      <c r="J13">
+        <v>353.38</v>
+      </c>
+      <c r="K13">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>1205</v>
+      </c>
+      <c r="D14">
+        <v>27.4</v>
+      </c>
+      <c r="E14">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F14">
+        <v>163</v>
+      </c>
+      <c r="G14">
+        <v>163</v>
+      </c>
+      <c r="H14">
+        <v>163</v>
+      </c>
+      <c r="I14">
+        <v>163</v>
+      </c>
+      <c r="J14">
+        <v>163</v>
+      </c>
+      <c r="K14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>58</v>
+      </c>
+      <c r="D15">
+        <v>3.6</v>
+      </c>
+      <c r="E15">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F15">
+        <v>299.25</v>
+      </c>
+      <c r="G15">
+        <v>299.25</v>
+      </c>
+      <c r="H15">
+        <v>299.25</v>
+      </c>
+      <c r="I15">
+        <v>299.25</v>
+      </c>
+      <c r="J15">
+        <v>299.25</v>
+      </c>
+      <c r="K15">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>187</v>
+      </c>
+      <c r="D16">
+        <v>14.5</v>
+      </c>
+      <c r="E16">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F16">
+        <v>321.25</v>
+      </c>
+      <c r="G16">
+        <v>321.25</v>
+      </c>
+      <c r="H16">
+        <v>321.25</v>
+      </c>
+      <c r="I16">
+        <v>321.25</v>
+      </c>
+      <c r="J16">
+        <v>321.25</v>
+      </c>
+      <c r="K16">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>142.47999999999999</v>
+      </c>
+      <c r="D17">
+        <v>3.2479999999999989</v>
+      </c>
+      <c r="E17">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F17">
+        <v>265.75</v>
+      </c>
+      <c r="G17">
+        <v>265.75</v>
+      </c>
+      <c r="H17">
+        <v>265.75</v>
+      </c>
+      <c r="I17">
+        <v>265.75</v>
+      </c>
+      <c r="J17">
+        <v>265.75</v>
+      </c>
+      <c r="K17">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18">
+        <v>5.4</v>
+      </c>
+      <c r="D18">
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F18">
+        <v>180.93</v>
+      </c>
+      <c r="G18">
+        <v>180.93</v>
+      </c>
+      <c r="H18">
+        <v>180.93</v>
+      </c>
+      <c r="I18">
+        <v>180.93</v>
+      </c>
+      <c r="J18">
+        <v>180.93</v>
+      </c>
+      <c r="K18">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19">
+        <v>379.8</v>
+      </c>
+      <c r="D19">
+        <v>8.6799999999999962</v>
+      </c>
+      <c r="E19">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F19">
+        <v>353.38</v>
+      </c>
+      <c r="G19">
+        <v>353.38</v>
+      </c>
+      <c r="H19">
+        <v>353.38</v>
+      </c>
+      <c r="I19">
+        <v>353.38</v>
+      </c>
+      <c r="J19">
+        <v>353.38</v>
+      </c>
+      <c r="K19">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20">
+        <v>1342</v>
+      </c>
+      <c r="D20">
+        <v>27.4</v>
+      </c>
+      <c r="E20">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F20">
+        <v>163</v>
+      </c>
+      <c r="G20">
+        <v>163</v>
+      </c>
+      <c r="H20">
+        <v>163</v>
+      </c>
+      <c r="I20">
+        <v>163</v>
+      </c>
+      <c r="J20">
+        <v>163</v>
+      </c>
+      <c r="K20">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
+        <v>76</v>
+      </c>
+      <c r="D21">
+        <v>3.6</v>
+      </c>
+      <c r="E21">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F21">
+        <v>299.25</v>
+      </c>
+      <c r="G21">
+        <v>299.25</v>
+      </c>
+      <c r="H21">
+        <v>299.25</v>
+      </c>
+      <c r="I21">
+        <v>299.25</v>
+      </c>
+      <c r="J21">
+        <v>299.25</v>
+      </c>
+      <c r="K21">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>259.5</v>
+      </c>
+      <c r="D22">
+        <v>14.5</v>
+      </c>
+      <c r="E22">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F22">
+        <v>321.25</v>
+      </c>
+      <c r="G22">
+        <v>321.25</v>
+      </c>
+      <c r="H22">
+        <v>321.25</v>
+      </c>
+      <c r="I22">
+        <v>321.25</v>
+      </c>
+      <c r="J22">
+        <v>321.25</v>
+      </c>
+      <c r="K22">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23">
+        <v>158.72</v>
+      </c>
+      <c r="D23">
+        <v>3.2479999999999989</v>
+      </c>
+      <c r="E23">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F23">
+        <v>265.75</v>
+      </c>
+      <c r="G23">
+        <v>265.75</v>
+      </c>
+      <c r="H23">
+        <v>265.75</v>
+      </c>
+      <c r="I23">
+        <v>265.75</v>
+      </c>
+      <c r="J23">
+        <v>265.75</v>
+      </c>
+      <c r="K23">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>6.4</v>
+      </c>
+      <c r="D24">
+        <v>0.2</v>
+      </c>
+      <c r="E24">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F24">
+        <v>180.93</v>
+      </c>
+      <c r="G24">
+        <v>180.93</v>
+      </c>
+      <c r="H24">
+        <v>180.93</v>
+      </c>
+      <c r="I24">
+        <v>180.93</v>
+      </c>
+      <c r="J24">
+        <v>180.93</v>
+      </c>
+      <c r="K24">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25">
+        <v>423.19999999999987</v>
+      </c>
+      <c r="D25">
+        <v>8.6799999999999962</v>
+      </c>
+      <c r="E25">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F25">
+        <v>353.38</v>
+      </c>
+      <c r="G25">
+        <v>353.38</v>
+      </c>
+      <c r="H25">
+        <v>353.38</v>
+      </c>
+      <c r="I25">
+        <v>353.38</v>
+      </c>
+      <c r="J25">
+        <v>353.38</v>
+      </c>
+      <c r="K25">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26">
+        <v>1479</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F26">
+        <v>163</v>
+      </c>
+      <c r="G26">
+        <v>163</v>
+      </c>
+      <c r="H26">
+        <v>163</v>
+      </c>
+      <c r="I26">
+        <v>163</v>
+      </c>
+      <c r="J26">
+        <v>163</v>
+      </c>
+      <c r="K26">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27">
+        <v>94</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F27">
+        <v>299.25</v>
+      </c>
+      <c r="G27">
+        <v>299.25</v>
+      </c>
+      <c r="H27">
+        <v>299.25</v>
+      </c>
+      <c r="I27">
+        <v>299.25</v>
+      </c>
+      <c r="J27">
+        <v>299.25</v>
+      </c>
+      <c r="K27">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28">
+        <v>332</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F28">
+        <v>321.25</v>
+      </c>
+      <c r="G28">
+        <v>321.25</v>
+      </c>
+      <c r="H28">
+        <v>321.25</v>
+      </c>
+      <c r="I28">
+        <v>321.25</v>
+      </c>
+      <c r="J28">
+        <v>321.25</v>
+      </c>
+      <c r="K28">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29">
+        <v>174.96</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F29">
+        <v>265.75</v>
+      </c>
+      <c r="G29">
+        <v>265.75</v>
+      </c>
+      <c r="H29">
+        <v>265.75</v>
+      </c>
+      <c r="I29">
+        <v>265.75</v>
+      </c>
+      <c r="J29">
+        <v>265.75</v>
+      </c>
+      <c r="K29">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30">
+        <v>7.4</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F30">
+        <v>180.93</v>
+      </c>
+      <c r="G30">
+        <v>180.93</v>
+      </c>
+      <c r="H30">
+        <v>180.93</v>
+      </c>
+      <c r="I30">
+        <v>180.93</v>
+      </c>
+      <c r="J30">
+        <v>180.93</v>
+      </c>
+      <c r="K30">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
+        <v>466.59999999999991</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F31">
+        <v>353.38</v>
+      </c>
+      <c r="G31">
+        <v>353.38</v>
+      </c>
+      <c r="H31">
+        <v>353.38</v>
+      </c>
+      <c r="I31">
+        <v>353.38</v>
+      </c>
+      <c r="J31">
+        <v>353.38</v>
+      </c>
+      <c r="K31">
+        <v>353.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B907D735-A300-49B9-83F4-46BAB72A5CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2646577E-9061-41EB-96C3-5DD2EFBFCD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="3285" windowWidth="31530" windowHeight="16905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5535" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="regions" sheetId="2" r:id="rId2"/>
     <sheet name="params_region" sheetId="3" r:id="rId3"/>
-    <sheet name="c_ship" sheetId="4" r:id="rId4"/>
-    <sheet name="README" sheetId="5" r:id="rId5"/>
-    <sheet name="Tabelle1" sheetId="6" r:id="rId6"/>
+    <sheet name="params_region_low" sheetId="10" r:id="rId4"/>
+    <sheet name="c_ship" sheetId="4" r:id="rId5"/>
+    <sheet name="README" sheetId="5" r:id="rId6"/>
     <sheet name="initial_state" sheetId="7" r:id="rId7"/>
+    <sheet name="research" sheetId="8" r:id="rId8"/>
+    <sheet name="old_demand" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -188,8 +190,158 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{47F665BF-8293-4D3E-B9BD-15A1A4536E3D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Full-demand threshold price p_full, set equal to regional WTP in USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{F70412CF-6507-46F0-BF56-AEF1F2975E26}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Absolute value of demand elasticity used for base calibration scenario.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{FCE5DF1B-2AF5-4476-AE75-8D097E24C44F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{79301CAF-0844-4AB3-A488-2B33C92AEB7A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{E6F3FA0E-741B-4A5F-BE0E-3802D8F1A660}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{24E7A962-F2BD-4A2A-B332-6B2A989D1107}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{B5C7AA7C-996E-4C07-98B4-8833BF33F141}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2025 = p_full/(eps_abs_base*dmax_2025). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{8358BC5C-8508-4B09-9CB8-40DEABBD2C87}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2030 = p_full/(eps_abs_base*dmax_2030). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{E9803227-9B53-44D4-8EC8-50C532D94382}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2035 = p_full/(eps_abs_base*dmax_2035). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{8B5EDABB-505A-4F78-807E-8735E6DB3744}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2040 = p_full/(eps_abs_base*dmax_2040). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
   <si>
     <t>region</t>
   </si>
@@ -404,6 +556,30 @@
   <si>
     <t>2045</t>
   </si>
+  <si>
+    <t>Renewables 2025</t>
+  </si>
+  <si>
+    <t>china</t>
+  </si>
+  <si>
+    <t>2025-2030</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>Asia Pacific</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>ROW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from regioanal summaries </t>
+  </si>
 </sst>
 </file>
 
@@ -412,7 +588,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +613,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -501,10 +691,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -524,8 +715,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -539,6 +739,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>31623</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>753846</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95936</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B98F21F-83BC-6197-8112-B72E85A40C0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3695700" y="412623"/>
+          <a:ext cx="7726146" cy="3874313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -957,7 +1206,7 @@
       <c r="C2">
         <v>278</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="10">
         <v>410</v>
       </c>
       <c r="E2">
@@ -977,7 +1226,7 @@
         <v>2.5</v>
       </c>
       <c r="J2">
-        <v>27.4</v>
+        <v>200</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1037,7 +1286,7 @@
       <c r="C3">
         <v>58.99</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="10">
         <v>68</v>
       </c>
       <c r="E3">
@@ -1117,7 +1366,7 @@
       <c r="C4">
         <v>38.270000000000003</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="10">
         <v>70</v>
       </c>
       <c r="E4">
@@ -1197,7 +1446,7 @@
       <c r="C5">
         <v>49.08</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="11">
         <v>290</v>
       </c>
       <c r="E5">
@@ -1277,14 +1526,14 @@
       <c r="C6">
         <v>18.2</v>
       </c>
-      <c r="D6">
-        <v>33</v>
+      <c r="D6" s="12">
+        <v>75.56</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G6">
         <v>180.93</v>
@@ -1336,15 +1585,15 @@
       </c>
       <c r="U6" s="6">
         <f t="shared" si="3"/>
-        <v>38.235690235690235</v>
+        <v>16.699017704840887</v>
       </c>
       <c r="V6" s="6">
         <f t="shared" si="4"/>
-        <v>20.351254480286734</v>
+        <v>9.7059829059829053</v>
       </c>
       <c r="W6" s="6">
         <f t="shared" si="5"/>
-        <v>14.019753086419753</v>
+        <v>7.0098765432098764</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -1357,14 +1606,14 @@
       <c r="C7">
         <v>27.61</v>
       </c>
-      <c r="D7">
-        <v>90.56</v>
+      <c r="D7" s="10">
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>353.38</v>
@@ -1416,15 +1665,15 @@
       </c>
       <c r="U7" s="6">
         <f t="shared" si="3"/>
-        <v>11.895367098547309</v>
+        <v>71.816296296296301</v>
       </c>
       <c r="V7" s="6">
         <f t="shared" si="4"/>
-        <v>8.2864957264957262</v>
+        <v>17.374910394265232</v>
       </c>
       <c r="W7" s="6">
         <f t="shared" si="5"/>
-        <v>5.9846913580246914</v>
+        <v>11.969382716049383</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -1445,30 +1694,39 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-    </row>
-    <row r="24" spans="18:21" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.25">
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="18:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.25">
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="18:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
@@ -1481,6 +1739,660 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE89C27-BBF7-41CE-8C8B-5B3DD823E765}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="30.5703125" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="27.85546875" customWidth="1"/>
+    <col min="16" max="16" width="25.42578125" customWidth="1"/>
+    <col min="17" max="17" width="24.140625" customWidth="1"/>
+    <col min="18" max="18" width="22.85546875" customWidth="1"/>
+    <col min="19" max="19" width="28.5703125" customWidth="1"/>
+    <col min="20" max="20" width="31.85546875" customWidth="1"/>
+    <col min="21" max="21" width="31.42578125" customWidth="1"/>
+    <col min="22" max="22" width="42.7109375" customWidth="1"/>
+    <col min="23" max="23" width="38.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>931</v>
+      </c>
+      <c r="C2">
+        <v>278</v>
+      </c>
+      <c r="D2">
+        <v>420</v>
+      </c>
+      <c r="E2">
+        <f>D2*1.1</f>
+        <v>462.00000000000006</v>
+      </c>
+      <c r="F2">
+        <f>E2*1.1</f>
+        <v>508.2000000000001</v>
+      </c>
+      <c r="G2">
+        <v>163</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I7" si="0">H2*0.05</f>
+        <v>2.5</v>
+      </c>
+      <c r="J2">
+        <v>27.4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1000</v>
+      </c>
+      <c r="M2">
+        <v>1E-3</v>
+      </c>
+      <c r="N2" s="5">
+        <v>521.41999999999996</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P2" s="5">
+        <f t="shared" ref="P2:S7" si="1">$N2*(1+1/$O2)</f>
+        <v>1100.7755555555555</v>
+      </c>
+      <c r="Q2" s="5">
+        <f t="shared" si="1"/>
+        <v>1100.7755555555555</v>
+      </c>
+      <c r="R2" s="5">
+        <f t="shared" si="1"/>
+        <v>1100.7755555555555</v>
+      </c>
+      <c r="S2" s="5">
+        <f t="shared" si="1"/>
+        <v>1100.7755555555555</v>
+      </c>
+      <c r="T2" s="6">
+        <f t="shared" ref="T2:T7" si="2">$N2/($O2*$C2)</f>
+        <v>2.084012789768185</v>
+      </c>
+      <c r="U2" s="6">
+        <f t="shared" ref="U2:U7" si="3">$N2/($O2*$D2)</f>
+        <v>1.3794179894179892</v>
+      </c>
+      <c r="V2" s="6">
+        <f t="shared" ref="V2:V7" si="4">$N2/($O2*$E2)</f>
+        <v>1.2540163540163538</v>
+      </c>
+      <c r="W2" s="6">
+        <f t="shared" ref="W2:W7" si="5">$N2/($O2*$F2)</f>
+        <v>1.1400148672875943</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>58.99</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:F7" si="6">D3*1.1</f>
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="6"/>
+        <v>96.800000000000011</v>
+      </c>
+      <c r="G3">
+        <v>299.25</v>
+      </c>
+      <c r="H3">
+        <v>175</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="J3">
+        <v>3.6</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1000</v>
+      </c>
+      <c r="M3">
+        <v>1E-3</v>
+      </c>
+      <c r="N3" s="5">
+        <v>967.65</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P3" s="5">
+        <f t="shared" si="1"/>
+        <v>2042.8166666666666</v>
+      </c>
+      <c r="Q3" s="5">
+        <f t="shared" si="1"/>
+        <v>2042.8166666666666</v>
+      </c>
+      <c r="R3" s="5">
+        <f t="shared" si="1"/>
+        <v>2042.8166666666666</v>
+      </c>
+      <c r="S3" s="5">
+        <f t="shared" si="1"/>
+        <v>2042.8166666666666</v>
+      </c>
+      <c r="T3" s="6">
+        <f t="shared" si="2"/>
+        <v>18.226253037237949</v>
+      </c>
+      <c r="U3" s="6">
+        <f t="shared" si="3"/>
+        <v>13.439583333333333</v>
+      </c>
+      <c r="V3" s="6">
+        <f t="shared" si="4"/>
+        <v>12.217803030303029</v>
+      </c>
+      <c r="W3" s="6">
+        <f t="shared" si="5"/>
+        <v>11.107093663911844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>38.270000000000003</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="6"/>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="6"/>
+        <v>121.00000000000003</v>
+      </c>
+      <c r="G4">
+        <v>321.25</v>
+      </c>
+      <c r="H4">
+        <v>175</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="J4">
+        <v>14.5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1000</v>
+      </c>
+      <c r="M4">
+        <v>1E-3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>561.07000000000005</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P4" s="5">
+        <f t="shared" si="1"/>
+        <v>1184.4811111111112</v>
+      </c>
+      <c r="Q4" s="5">
+        <f t="shared" si="1"/>
+        <v>1184.4811111111112</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" si="1"/>
+        <v>1184.4811111111112</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" si="1"/>
+        <v>1184.4811111111112</v>
+      </c>
+      <c r="T4" s="6">
+        <f t="shared" si="2"/>
+        <v>16.289812153412885</v>
+      </c>
+      <c r="U4" s="6">
+        <f t="shared" si="3"/>
+        <v>6.2341111111111118</v>
+      </c>
+      <c r="V4" s="6">
+        <f t="shared" si="4"/>
+        <v>5.6673737373737367</v>
+      </c>
+      <c r="W4" s="6">
+        <f t="shared" si="5"/>
+        <v>5.1521579430670332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>110</v>
+      </c>
+      <c r="C5">
+        <v>49.08</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="6"/>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="6"/>
+        <v>60.500000000000014</v>
+      </c>
+      <c r="G5">
+        <v>265.75</v>
+      </c>
+      <c r="H5">
+        <v>57.5</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>2.875</v>
+      </c>
+      <c r="J5">
+        <v>3.2479999999999989</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1000</v>
+      </c>
+      <c r="M5">
+        <v>1E-3</v>
+      </c>
+      <c r="N5" s="5">
+        <v>534.14</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P5" s="5">
+        <f t="shared" si="1"/>
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" si="1"/>
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="1"/>
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="1"/>
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="T5" s="6">
+        <f t="shared" si="2"/>
+        <v>12.092275649732862</v>
+      </c>
+      <c r="U5" s="6">
+        <f t="shared" si="3"/>
+        <v>11.869777777777777</v>
+      </c>
+      <c r="V5" s="6">
+        <f t="shared" si="4"/>
+        <v>10.790707070707068</v>
+      </c>
+      <c r="W5" s="6">
+        <f t="shared" si="5"/>
+        <v>9.8097337006427878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>3.4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>7.8</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="6"/>
+        <v>8.58</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="6"/>
+        <v>9.4380000000000006</v>
+      </c>
+      <c r="G6">
+        <v>180.93</v>
+      </c>
+      <c r="H6">
+        <v>150</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>1E-3</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1135.5999999999999</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P6" s="5">
+        <f t="shared" si="1"/>
+        <v>2397.3777777777777</v>
+      </c>
+      <c r="Q6" s="5">
+        <f t="shared" si="1"/>
+        <v>2397.3777777777777</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="1"/>
+        <v>2397.3777777777777</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="1"/>
+        <v>2397.3777777777777</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" si="2"/>
+        <v>420.59259259259255</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" si="3"/>
+        <v>161.76638176638176</v>
+      </c>
+      <c r="V6" s="6">
+        <f t="shared" si="4"/>
+        <v>147.06034706034703</v>
+      </c>
+      <c r="W6" s="6">
+        <f t="shared" si="5"/>
+        <v>133.69122460031548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>293</v>
+      </c>
+      <c r="C7">
+        <v>27.61</v>
+      </c>
+      <c r="D7">
+        <v>128</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="6"/>
+        <v>140.80000000000001</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="6"/>
+        <v>154.88000000000002</v>
+      </c>
+      <c r="G7">
+        <v>353.38</v>
+      </c>
+      <c r="H7">
+        <v>125</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="J7">
+        <v>8.6799999999999962</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1E-3</v>
+      </c>
+      <c r="N7" s="5">
+        <v>969.52</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="P7" s="5">
+        <f t="shared" si="1"/>
+        <v>2046.7644444444445</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="1"/>
+        <v>2046.7644444444445</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="1"/>
+        <v>2046.7644444444445</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="1"/>
+        <v>2046.7644444444445</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="2"/>
+        <v>39.016459414865786</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="3"/>
+        <v>8.4159722222222211</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="4"/>
+        <v>7.6508838383838373</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="5"/>
+        <v>6.9553489439853067</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C19" s="5"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C26" s="5"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1651,7 +2563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1668,46 +2580,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="C8:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C9">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C10">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C11">
-        <v>3.2479999999999989</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C13">
-        <v>8.6799999999999962</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1773,7 +2645,7 @@
         <v>931</v>
       </c>
       <c r="D2">
-        <v>27.4</v>
+        <v>13.7</v>
       </c>
       <c r="E2">
         <v>1100.775555555555</v>
@@ -1808,7 +2680,7 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="E3">
         <v>2042.8166666666671</v>
@@ -1843,7 +2715,7 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>14.5</v>
+        <v>7.25</v>
       </c>
       <c r="E4">
         <v>1184.481111111111</v>
@@ -1878,7 +2750,7 @@
         <v>110</v>
       </c>
       <c r="D5">
-        <v>3.2479999999999989</v>
+        <v>1.6239999999999994</v>
       </c>
       <c r="E5">
         <v>1127.6288888888889</v>
@@ -1913,7 +2785,7 @@
         <v>3.4</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E6">
         <v>2397.3777777777782</v>
@@ -1948,7 +2820,7 @@
         <v>293</v>
       </c>
       <c r="D7">
-        <v>8.6799999999999962</v>
+        <v>4.3399999999999981</v>
       </c>
       <c r="E7">
         <v>2046.764444444445</v>
@@ -1983,7 +2855,7 @@
         <v>1068</v>
       </c>
       <c r="D8">
-        <v>27.4</v>
+        <v>13.7</v>
       </c>
       <c r="E8">
         <v>1100.775555555555</v>
@@ -2018,7 +2890,7 @@
         <v>40</v>
       </c>
       <c r="D9">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9">
         <v>2042.8166666666671</v>
@@ -2053,7 +2925,7 @@
         <v>114.5</v>
       </c>
       <c r="D10">
-        <v>14.5</v>
+        <v>7.25</v>
       </c>
       <c r="E10">
         <v>1184.481111111111</v>
@@ -2088,7 +2960,7 @@
         <v>126.24</v>
       </c>
       <c r="D11">
-        <v>3.2479999999999989</v>
+        <v>1.6239999999999994</v>
       </c>
       <c r="E11">
         <v>1127.6288888888889</v>
@@ -2123,7 +2995,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="D12">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
         <v>2397.3777777777782</v>
@@ -2158,7 +3030,7 @@
         <v>336.4</v>
       </c>
       <c r="D13">
-        <v>8.6799999999999962</v>
+        <v>4.3399999999999981</v>
       </c>
       <c r="E13">
         <v>2046.764444444445</v>
@@ -2193,7 +3065,7 @@
         <v>1205</v>
       </c>
       <c r="D14">
-        <v>27.4</v>
+        <v>13.7</v>
       </c>
       <c r="E14">
         <v>1100.775555555555</v>
@@ -2228,7 +3100,7 @@
         <v>58</v>
       </c>
       <c r="D15">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="E15">
         <v>2042.8166666666671</v>
@@ -2263,7 +3135,7 @@
         <v>187</v>
       </c>
       <c r="D16">
-        <v>14.5</v>
+        <v>7.25</v>
       </c>
       <c r="E16">
         <v>1184.481111111111</v>
@@ -2298,7 +3170,7 @@
         <v>142.47999999999999</v>
       </c>
       <c r="D17">
-        <v>3.2479999999999989</v>
+        <v>1.6239999999999994</v>
       </c>
       <c r="E17">
         <v>1127.6288888888889</v>
@@ -2333,7 +3205,7 @@
         <v>5.4</v>
       </c>
       <c r="D18">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E18">
         <v>2397.3777777777782</v>
@@ -2368,7 +3240,7 @@
         <v>379.8</v>
       </c>
       <c r="D19">
-        <v>8.6799999999999962</v>
+        <v>4.3399999999999981</v>
       </c>
       <c r="E19">
         <v>2046.764444444445</v>
@@ -2403,7 +3275,7 @@
         <v>1342</v>
       </c>
       <c r="D20">
-        <v>27.4</v>
+        <v>13.7</v>
       </c>
       <c r="E20">
         <v>1100.775555555555</v>
@@ -2438,7 +3310,7 @@
         <v>76</v>
       </c>
       <c r="D21">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21">
         <v>2042.8166666666671</v>
@@ -2473,7 +3345,7 @@
         <v>259.5</v>
       </c>
       <c r="D22">
-        <v>14.5</v>
+        <v>7.25</v>
       </c>
       <c r="E22">
         <v>1184.481111111111</v>
@@ -2508,7 +3380,7 @@
         <v>158.72</v>
       </c>
       <c r="D23">
-        <v>3.2479999999999989</v>
+        <v>1.6239999999999994</v>
       </c>
       <c r="E23">
         <v>1127.6288888888889</v>
@@ -2543,7 +3415,7 @@
         <v>6.4</v>
       </c>
       <c r="D24">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E24">
         <v>2397.3777777777782</v>
@@ -2578,7 +3450,7 @@
         <v>423.19999999999987</v>
       </c>
       <c r="D25">
-        <v>8.6799999999999962</v>
+        <v>4.3399999999999981</v>
       </c>
       <c r="E25">
         <v>2046.764444444445</v>
@@ -2815,4 +3687,232 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1202B3F-7149-466F-A577-400076578845}">
+  <dimension ref="B3:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="5">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="https://iea.blob.core.windows.net/assets/76ad6eac-2aa6-4c55-9a55-b8dc0dba9f9e/Renewables2025.pdf" xr:uid="{A2FF3907-04B2-401A-98BB-94A01FAAFFB7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D456399-6888-4EF0-98EA-DC50B5E85FC9}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>931</v>
+      </c>
+      <c r="C2">
+        <v>278</v>
+      </c>
+      <c r="D2">
+        <v>410</v>
+      </c>
+      <c r="E2">
+        <v>540</v>
+      </c>
+      <c r="F2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>58.99</v>
+      </c>
+      <c r="D3">
+        <v>68</v>
+      </c>
+      <c r="E3">
+        <v>145</v>
+      </c>
+      <c r="F3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>38.270000000000003</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>95</v>
+      </c>
+      <c r="F4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>110</v>
+      </c>
+      <c r="C5">
+        <v>49.08</v>
+      </c>
+      <c r="D5">
+        <v>290</v>
+      </c>
+      <c r="E5">
+        <v>375</v>
+      </c>
+      <c r="F5">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>3.4</v>
+      </c>
+      <c r="C6">
+        <v>18.2</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
+      <c r="E6">
+        <v>62</v>
+      </c>
+      <c r="F6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>293</v>
+      </c>
+      <c r="C7">
+        <v>27.61</v>
+      </c>
+      <c r="D7">
+        <v>90.56</v>
+      </c>
+      <c r="E7">
+        <v>130</v>
+      </c>
+      <c r="F7">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2646577E-9061-41EB-96C3-5DD2EFBFCD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03F324-8070-4E0D-88B7-3FE15D07D223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="regions" sheetId="2" r:id="rId2"/>
     <sheet name="params_region" sheetId="3" r:id="rId3"/>
-    <sheet name="params_region_low" sheetId="10" r:id="rId4"/>
+    <sheet name="params_region_new" sheetId="10" r:id="rId4"/>
     <sheet name="c_ship" sheetId="4" r:id="rId5"/>
     <sheet name="README" sheetId="5" r:id="rId6"/>
     <sheet name="initial_state" sheetId="7" r:id="rId7"/>
@@ -1524,16 +1524,16 @@
         <v>3.4</v>
       </c>
       <c r="C6">
-        <v>18.2</v>
-      </c>
-      <c r="D6" s="12">
-        <v>75.56</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="10">
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>180.93</v>
@@ -1581,18 +1581,18 @@
       </c>
       <c r="T6" s="6">
         <f t="shared" si="2"/>
-        <v>69.328449328449324</v>
+        <v>252.35555555555553</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" si="3"/>
+        <f>$N6/($O6*$D7)</f>
         <v>16.699017704840887</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" si="4"/>
+        <f>$N6/($O6*$E7)</f>
         <v>9.7059829059829053</v>
       </c>
       <c r="W6" s="6">
-        <f t="shared" si="5"/>
+        <f>$N6/($O6*$F7)</f>
         <v>7.0098765432098764</v>
       </c>
     </row>
@@ -1606,14 +1606,14 @@
       <c r="C7">
         <v>27.61</v>
       </c>
-      <c r="D7" s="10">
-        <v>15</v>
+      <c r="D7" s="12">
+        <v>75.56</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G7">
         <v>353.38</v>
@@ -1664,15 +1664,15 @@
         <v>39.016459414865786</v>
       </c>
       <c r="U7" s="6">
-        <f t="shared" si="3"/>
+        <f>$N7/($O7*$D6)</f>
         <v>71.816296296296301</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="4"/>
+        <f>$N7/($O7*$E6)</f>
         <v>17.374910394265232</v>
       </c>
       <c r="W7" s="6">
-        <f t="shared" si="5"/>
+        <f>$N7/($O7*$F6)</f>
         <v>11.969382716049383</v>
       </c>
     </row>
@@ -1846,18 +1846,16 @@
         <v>931</v>
       </c>
       <c r="C2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D2">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="E2">
-        <f>D2*1.1</f>
-        <v>462.00000000000006</v>
+        <v>333</v>
       </c>
       <c r="F2">
-        <f>E2*1.1</f>
-        <v>508.2000000000001</v>
+        <v>316</v>
       </c>
       <c r="G2">
         <v>163</v>
@@ -1905,19 +1903,19 @@
       </c>
       <c r="T2" s="6">
         <f t="shared" ref="T2:T7" si="2">$N2/($O2*$C2)</f>
-        <v>2.084012789768185</v>
+        <v>2.0691269841269841</v>
       </c>
       <c r="U2" s="6">
         <f t="shared" ref="U2:U7" si="3">$N2/($O2*$D2)</f>
-        <v>1.3794179894179892</v>
+        <v>1.6553015873015873</v>
       </c>
       <c r="V2" s="6">
         <f t="shared" ref="V2:V7" si="4">$N2/($O2*$E2)</f>
-        <v>1.2540163540163538</v>
+        <v>1.7398064731398064</v>
       </c>
       <c r="W2" s="6">
         <f t="shared" ref="W2:W7" si="5">$N2/($O2*$F2)</f>
-        <v>1.1400148672875943</v>
+        <v>1.8334036568213781</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -1928,18 +1926,16 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>58.99</v>
+        <v>75</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:F7" si="6">D3*1.1</f>
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F3">
-        <f t="shared" si="6"/>
-        <v>96.800000000000011</v>
+        <v>99</v>
       </c>
       <c r="G3">
         <v>299.25</v>
@@ -1952,7 +1948,7 @@
         <v>8.75</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1985,21 +1981,21 @@
         <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="T3" s="6">
-        <f t="shared" si="2"/>
-        <v>18.226253037237949</v>
-      </c>
-      <c r="U3" s="6">
-        <f t="shared" si="3"/>
-        <v>13.439583333333333</v>
-      </c>
-      <c r="V3" s="6">
-        <f t="shared" si="4"/>
-        <v>12.217803030303029</v>
-      </c>
-      <c r="W3" s="6">
-        <f t="shared" si="5"/>
-        <v>11.107093663911844</v>
+      <c r="T3" s="6" t="e">
+        <f>$N3/($O3*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U3" s="6" t="e">
+        <f>$N3/($O3*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V3" s="6" t="e">
+        <f>$N3/($O3*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W3" s="6" t="e">
+        <f>$N3/($O3*#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -2010,18 +2006,16 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>38.270000000000003</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E4">
-        <f t="shared" si="6"/>
-        <v>110.00000000000001</v>
+        <v>70</v>
       </c>
       <c r="F4">
-        <f t="shared" si="6"/>
-        <v>121.00000000000003</v>
+        <v>75</v>
       </c>
       <c r="G4">
         <v>321.25</v>
@@ -2034,7 +2028,7 @@
         <v>8.75</v>
       </c>
       <c r="J4">
-        <v>14.5</v>
+        <v>5.33</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2067,21 +2061,21 @@
         <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="T4" s="6">
-        <f t="shared" si="2"/>
-        <v>16.289812153412885</v>
-      </c>
-      <c r="U4" s="6">
-        <f t="shared" si="3"/>
-        <v>6.2341111111111118</v>
-      </c>
-      <c r="V4" s="6">
-        <f t="shared" si="4"/>
-        <v>5.6673737373737367</v>
-      </c>
-      <c r="W4" s="6">
-        <f t="shared" si="5"/>
-        <v>5.1521579430670332</v>
+      <c r="T4" s="6" t="e">
+        <f>$N4/($O4*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U4" s="6" t="e">
+        <f>$N4/($O4*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V4" s="6" t="e">
+        <f>$N4/($O4*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W4" s="6" t="e">
+        <f>$N4/($O4*#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -2092,18 +2086,16 @@
         <v>110</v>
       </c>
       <c r="C5">
-        <v>49.08</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E5">
-        <f t="shared" si="6"/>
-        <v>55.000000000000007</v>
+        <v>103</v>
       </c>
       <c r="F5">
-        <f t="shared" si="6"/>
-        <v>60.500000000000014</v>
+        <v>126</v>
       </c>
       <c r="G5">
         <v>265.75</v>
@@ -2116,7 +2108,7 @@
         <v>2.875</v>
       </c>
       <c r="J5">
-        <v>3.2479999999999989</v>
+        <v>12.67</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2149,21 +2141,21 @@
         <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="T5" s="6">
-        <f t="shared" si="2"/>
-        <v>12.092275649732862</v>
-      </c>
-      <c r="U5" s="6">
-        <f t="shared" si="3"/>
-        <v>11.869777777777777</v>
-      </c>
-      <c r="V5" s="6">
-        <f t="shared" si="4"/>
-        <v>10.790707070707068</v>
-      </c>
-      <c r="W5" s="6">
-        <f t="shared" si="5"/>
-        <v>9.8097337006427878</v>
+      <c r="T5" s="6" t="e">
+        <f>$N5/($O5*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U5" s="6" t="e">
+        <f>$N5/($O5*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V5" s="6" t="e">
+        <f>$N5/($O5*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W5" s="6" t="e">
+        <f>$N5/($O5*#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -2174,18 +2166,16 @@
         <v>3.4</v>
       </c>
       <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5">
-        <v>7.8</v>
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6">
-        <f t="shared" si="6"/>
-        <v>8.58</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <f t="shared" si="6"/>
-        <v>9.4380000000000006</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>180.93</v>
@@ -2198,7 +2188,7 @@
         <v>7.5</v>
       </c>
       <c r="J6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -2231,21 +2221,21 @@
         <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="T6" s="6">
-        <f t="shared" si="2"/>
-        <v>420.59259259259255</v>
-      </c>
-      <c r="U6" s="6">
-        <f t="shared" si="3"/>
-        <v>161.76638176638176</v>
-      </c>
-      <c r="V6" s="6">
-        <f t="shared" si="4"/>
-        <v>147.06034706034703</v>
-      </c>
-      <c r="W6" s="6">
-        <f t="shared" si="5"/>
-        <v>133.69122460031548</v>
+      <c r="T6" s="6" t="e">
+        <f>$N6/($O6*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U6" s="6" t="e">
+        <f>$N6/($O6*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V6" s="6" t="e">
+        <f>$N6/($O6*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W6" s="6" t="e">
+        <f>$N6/($O6*#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -2256,18 +2246,16 @@
         <v>293</v>
       </c>
       <c r="C7">
-        <v>27.61</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E7">
-        <f t="shared" si="6"/>
-        <v>140.80000000000001</v>
+        <v>79</v>
       </c>
       <c r="F7">
-        <f t="shared" si="6"/>
-        <v>154.88000000000002</v>
+        <v>89</v>
       </c>
       <c r="G7">
         <v>353.38</v>
@@ -2280,7 +2268,7 @@
         <v>6.25</v>
       </c>
       <c r="J7">
-        <v>8.6799999999999962</v>
+        <v>4.33</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -2313,21 +2301,21 @@
         <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="T7" s="6">
-        <f t="shared" si="2"/>
-        <v>39.016459414865786</v>
-      </c>
-      <c r="U7" s="6">
-        <f t="shared" si="3"/>
-        <v>8.4159722222222211</v>
-      </c>
-      <c r="V7" s="6">
-        <f t="shared" si="4"/>
-        <v>7.6508838383838373</v>
-      </c>
-      <c r="W7" s="6">
-        <f t="shared" si="5"/>
-        <v>6.9553489439853067</v>
+      <c r="T7" s="6" t="e">
+        <f>$N7/($O7*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U7" s="6" t="e">
+        <f>$N7/($O7*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V7" s="6" t="e">
+        <f>$N7/($O7*#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W7" s="6" t="e">
+        <f>$N7/($O7*#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -2388,7 +2376,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03F324-8070-4E0D-88B7-3FE15D07D223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21702A02-F86E-43C4-97DE-1A5FE1766CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -1226,7 +1226,7 @@
         <v>2.5</v>
       </c>
       <c r="J2">
-        <v>200</v>
+        <v>27.4</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1264,15 +1264,15 @@
         <v>2.084012789768185</v>
       </c>
       <c r="U2" s="6">
-        <f t="shared" ref="U2:U7" si="3">$N2/($O2*$D2)</f>
+        <f t="shared" ref="U2:U5" si="3">$N2/($O2*$D2)</f>
         <v>1.4130623306233061</v>
       </c>
       <c r="V2" s="6">
-        <f t="shared" ref="V2:V7" si="4">$N2/($O2*$E2)</f>
+        <f t="shared" ref="V2:V5" si="4">$N2/($O2*$E2)</f>
         <v>1.0728806584362138</v>
       </c>
       <c r="W2" s="6">
-        <f t="shared" ref="W2:W7" si="5">$N2/($O2*$F2)</f>
+        <f t="shared" ref="W2:W5" si="5">$N2/($O2*$F2)</f>
         <v>0.96559259259259256</v>
       </c>
     </row>
@@ -1902,20 +1902,16 @@
         <v>1100.7755555555555</v>
       </c>
       <c r="T2" s="6">
-        <f t="shared" ref="T2:T7" si="2">$N2/($O2*$C2)</f>
-        <v>2.0691269841269841</v>
+        <v>2.084012789768185</v>
       </c>
       <c r="U2" s="6">
-        <f t="shared" ref="U2:U7" si="3">$N2/($O2*$D2)</f>
-        <v>1.6553015873015873</v>
+        <v>1.4130623306233061</v>
       </c>
       <c r="V2" s="6">
-        <f t="shared" ref="V2:V7" si="4">$N2/($O2*$E2)</f>
-        <v>1.7398064731398064</v>
+        <v>1.0728806584362138</v>
       </c>
       <c r="W2" s="6">
-        <f t="shared" ref="W2:W7" si="5">$N2/($O2*$F2)</f>
-        <v>1.8334036568213781</v>
+        <v>0.96559259259259256</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -1981,21 +1977,17 @@
         <f t="shared" si="1"/>
         <v>2042.8166666666666</v>
       </c>
-      <c r="T3" s="6" t="e">
-        <f>$N3/($O3*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U3" s="6" t="e">
-        <f>$N3/($O3*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V3" s="6" t="e">
-        <f>$N3/($O3*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W3" s="6" t="e">
-        <f>$N3/($O3*#REF!)</f>
-        <v>#REF!</v>
+      <c r="T3" s="6">
+        <v>18.226253037237949</v>
+      </c>
+      <c r="U3" s="6">
+        <v>15.811274509803921</v>
+      </c>
+      <c r="V3" s="6">
+        <v>7.4149425287356321</v>
+      </c>
+      <c r="W3" s="6">
+        <v>4.3006666666666664</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -2061,21 +2053,17 @@
         <f t="shared" si="1"/>
         <v>1184.4811111111112</v>
       </c>
-      <c r="T4" s="6" t="e">
-        <f>$N4/($O4*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U4" s="6" t="e">
-        <f>$N4/($O4*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V4" s="6" t="e">
-        <f>$N4/($O4*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W4" s="6" t="e">
-        <f>$N4/($O4*#REF!)</f>
-        <v>#REF!</v>
+      <c r="T4" s="6">
+        <v>16.289812153412885</v>
+      </c>
+      <c r="U4" s="6">
+        <v>8.9058730158730164</v>
+      </c>
+      <c r="V4" s="6">
+        <v>6.5622222222222231</v>
+      </c>
+      <c r="W4" s="6">
+        <v>5.4209661835748797</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -2141,21 +2129,17 @@
         <f t="shared" si="1"/>
         <v>1127.6288888888889</v>
       </c>
-      <c r="T5" s="6" t="e">
-        <f>$N5/($O5*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U5" s="6" t="e">
-        <f>$N5/($O5*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V5" s="6" t="e">
-        <f>$N5/($O5*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W5" s="6" t="e">
-        <f>$N5/($O5*#REF!)</f>
-        <v>#REF!</v>
+      <c r="T5" s="6">
+        <v>12.092275649732862</v>
+      </c>
+      <c r="U5" s="6">
+        <v>2.046513409961686</v>
+      </c>
+      <c r="V5" s="6">
+        <v>1.5826370370370371</v>
+      </c>
+      <c r="W5" s="6">
+        <v>1.2901932367149758</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -2221,21 +2205,17 @@
         <f t="shared" si="1"/>
         <v>2397.3777777777777</v>
       </c>
-      <c r="T6" s="6" t="e">
-        <f>$N6/($O6*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U6" s="6" t="e">
-        <f>$N6/($O6*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V6" s="6" t="e">
-        <f>$N6/($O6*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W6" s="6" t="e">
-        <f>$N6/($O6*#REF!)</f>
-        <v>#REF!</v>
+      <c r="T6" s="6">
+        <v>252.35555555555553</v>
+      </c>
+      <c r="U6" s="6">
+        <v>16.699017704840887</v>
+      </c>
+      <c r="V6" s="6">
+        <v>9.7059829059829053</v>
+      </c>
+      <c r="W6" s="6">
+        <v>7.0098765432098764</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -2301,21 +2281,17 @@
         <f t="shared" si="1"/>
         <v>2046.7644444444445</v>
       </c>
-      <c r="T7" s="6" t="e">
-        <f>$N7/($O7*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U7" s="6" t="e">
-        <f>$N7/($O7*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="V7" s="6" t="e">
-        <f>$N7/($O7*#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W7" s="6" t="e">
-        <f>$N7/($O7*#REF!)</f>
-        <v>#REF!</v>
+      <c r="T7" s="6">
+        <v>39.016459414865786</v>
+      </c>
+      <c r="U7" s="6">
+        <v>71.816296296296301</v>
+      </c>
+      <c r="V7" s="6">
+        <v>17.374910394265232</v>
+      </c>
+      <c r="W7" s="6">
+        <v>11.969382716049383</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">

--- a/inputs/input_data_intertemporal.xlsx
+++ b/inputs/input_data_intertemporal.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21702A02-F86E-43C4-97DE-1A5FE1766CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0323A8A-AF47-4B25-A292-38F950D831ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="3975" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="2610" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="regions" sheetId="2" r:id="rId2"/>
-    <sheet name="params_region" sheetId="3" r:id="rId3"/>
-    <sheet name="params_region_new" sheetId="10" r:id="rId4"/>
-    <sheet name="c_ship" sheetId="4" r:id="rId5"/>
-    <sheet name="README" sheetId="5" r:id="rId6"/>
-    <sheet name="initial_state" sheetId="7" r:id="rId7"/>
+    <sheet name="params_region_new" sheetId="10" r:id="rId3"/>
+    <sheet name="c_ship" sheetId="4" r:id="rId4"/>
+    <sheet name="README" sheetId="5" r:id="rId5"/>
+    <sheet name="initial_state" sheetId="7" r:id="rId6"/>
+    <sheet name="initial_state_0" sheetId="11" r:id="rId7"/>
     <sheet name="research" sheetId="8" r:id="rId8"/>
     <sheet name="old_demand" sheetId="9" r:id="rId9"/>
+    <sheet name="params_region_OLD" sheetId="3" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,6 +42,156 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{47F665BF-8293-4D3E-B9BD-15A1A4536E3D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Full-demand threshold price p_full, set equal to regional WTP in USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{F70412CF-6507-46F0-BF56-AEF1F2975E26}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Absolute value of demand elasticity used for base calibration scenario.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{FCE5DF1B-2AF5-4476-AE75-8D097E24C44F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{79301CAF-0844-4AB3-A488-2B33C92AEB7A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{E6F3FA0E-741B-4A5F-BE0E-3802D8F1A660}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{24E7A962-F2BD-4A2A-B332-6B2A989D1107}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{B5C7AA7C-996E-4C07-98B4-8833BF33F141}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2025 = p_full/(eps_abs_base*dmax_2025). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{8358BC5C-8508-4B09-9CB8-40DEABBD2C87}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2030 = p_full/(eps_abs_base*dmax_2030). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{E9803227-9B53-44D4-8EC8-50C532D94382}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2035 = p_full/(eps_abs_base*dmax_2035). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{8B5EDABB-505A-4F78-807E-8735E6DB3744}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Inverse-demand slope b_dem_2040 = p_full/(eps_abs_base*dmax_2040). Unit: (USD/kW)/GW.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
@@ -190,158 +341,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{47F665BF-8293-4D3E-B9BD-15A1A4536E3D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Full-demand threshold price p_full, set equal to regional WTP in USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{F70412CF-6507-46F0-BF56-AEF1F2975E26}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Absolute value of demand elasticity used for base calibration scenario.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{FCE5DF1B-2AF5-4476-AE75-8D097E24C44F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{79301CAF-0844-4AB3-A488-2B33C92AEB7A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{E6F3FA0E-741B-4A5F-BE0E-3802D8F1A660}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{24E7A962-F2BD-4A2A-B332-6B2A989D1107}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand intercept a_dem = p_full*(1+1/eps_abs_base). Unit: USD/kW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{B5C7AA7C-996E-4C07-98B4-8833BF33F141}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand slope b_dem_2025 = p_full/(eps_abs_base*dmax_2025). Unit: (USD/kW)/GW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{8358BC5C-8508-4B09-9CB8-40DEABBD2C87}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand slope b_dem_2030 = p_full/(eps_abs_base*dmax_2030). Unit: (USD/kW)/GW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{E9803227-9B53-44D4-8EC8-50C532D94382}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand slope b_dem_2035 = p_full/(eps_abs_base*dmax_2035). Unit: (USD/kW)/GW.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{8B5EDABB-505A-4F78-807E-8735E6DB3744}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Inverse-demand slope b_dem_2040 = p_full/(eps_abs_base*dmax_2040). Unit: (USD/kW)/GW.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="75">
   <si>
     <t>region</t>
   </si>
@@ -1030,73 +1031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1738,7 +1673,73 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE89C27-BBF7-41CE-8C8B-5B3DD823E765}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1874,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M2">
         <v>1E-3</v>
@@ -1950,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M3">
         <v>1E-3</v>
@@ -2026,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M4">
         <v>1E-3</v>
@@ -2102,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M5">
         <v>1E-3</v>
@@ -2172,13 +2173,13 @@
         <v>7.5</v>
       </c>
       <c r="J6">
-        <v>0.93</v>
+        <v>0.5</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M6">
         <v>1E-3</v>
@@ -2254,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="M7">
         <v>1E-3</v>
@@ -2357,7 +2358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2528,7 +2529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2548,7 +2549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2817,7 +2818,7 @@
         <v>63</v>
       </c>
       <c r="C8">
-        <v>1068</v>
+        <v>931</v>
       </c>
       <c r="D8">
         <v>13.7</v>
@@ -2852,7 +2853,7 @@
         <v>63</v>
       </c>
       <c r="C9">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>1.8</v>
@@ -2887,7 +2888,7 @@
         <v>63</v>
       </c>
       <c r="C10">
-        <v>114.5</v>
+        <v>42</v>
       </c>
       <c r="D10">
         <v>7.25</v>
@@ -2922,7 +2923,7 @@
         <v>63</v>
       </c>
       <c r="C11">
-        <v>126.24</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>1.6239999999999994</v>
@@ -2957,7 +2958,7 @@
         <v>63</v>
       </c>
       <c r="C12">
-        <v>4.4000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="D12">
         <v>0.1</v>
@@ -2992,7 +2993,7 @@
         <v>63</v>
       </c>
       <c r="C13">
-        <v>336.4</v>
+        <v>293</v>
       </c>
       <c r="D13">
         <v>4.3399999999999981</v>
@@ -3027,7 +3028,7 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>1205</v>
+        <v>931</v>
       </c>
       <c r="D14">
         <v>13.7</v>
@@ -3062,7 +3063,7 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>1.8</v>
@@ -3097,7 +3098,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>7.25</v>
@@ -3132,7 +3133,7 @@
         <v>64</v>
       </c>
       <c r="C17">
-        <v>142.47999999999999</v>
+        <v>110</v>
       </c>
       <c r="D17">
         <v>1.6239999999999994</v>
@@ -3167,7 +3168,7 @@
         <v>64</v>
       </c>
       <c r="C18">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="D18">
         <v>0.1</v>
@@ -3202,7 +3203,7 @@
         <v>64</v>
       </c>
       <c r="C19">
-        <v>379.8</v>
+        <v>293</v>
       </c>
       <c r="D19">
         <v>4.3399999999999981</v>
@@ -3237,7 +3238,7 @@
         <v>65</v>
       </c>
       <c r="C20">
-        <v>1342</v>
+        <v>931</v>
       </c>
       <c r="D20">
         <v>13.7</v>
@@ -3272,7 +3273,7 @@
         <v>65</v>
       </c>
       <c r="C21">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>1.8</v>
@@ -3307,7 +3308,7 @@
         <v>65</v>
       </c>
       <c r="C22">
-        <v>259.5</v>
+        <v>42</v>
       </c>
       <c r="D22">
         <v>7.25</v>
@@ -3342,7 +3343,7 @@
         <v>65</v>
       </c>
       <c r="C23">
-        <v>158.72</v>
+        <v>110</v>
       </c>
       <c r="D23">
         <v>1.6239999999999994</v>
@@ -3377,7 +3378,7 @@
         <v>65</v>
       </c>
       <c r="C24">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="D24">
         <v>0.1</v>
@@ -3412,7 +3413,7 @@
         <v>65</v>
       </c>
       <c r="C25">
-        <v>423.19999999999987</v>
+        <v>293</v>
       </c>
       <c r="D25">
         <v>4.3399999999999981</v>
@@ -3447,10 +3448,10 @@
         <v>66</v>
       </c>
       <c r="C26">
-        <v>1479</v>
+        <v>931</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="E26">
         <v>1100.775555555555</v>
@@ -3482,10 +3483,10 @@
         <v>66</v>
       </c>
       <c r="C27">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E27">
         <v>2042.8166666666671</v>
@@ -3517,10 +3518,10 @@
         <v>66</v>
       </c>
       <c r="C28">
-        <v>332</v>
+        <v>42</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E28">
         <v>1184.481111111111</v>
@@ -3552,10 +3553,10 @@
         <v>66</v>
       </c>
       <c r="C29">
-        <v>174.96</v>
+        <v>110</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1.6239999999999994</v>
       </c>
       <c r="E29">
         <v>1127.6288888888889</v>
@@ -3587,10 +3588,10 @@
         <v>66</v>
       </c>
       <c r="C30">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E30">
         <v>2397.3777777777782</v>
@@ -3622,7 +3623,1112 @@
         <v>66</v>
       </c>
       <c r="C31">
-        <v>466.59999999999991</v>
+        <v>293</v>
+      </c>
+      <c r="D31">
+        <v>4.3399999999999981</v>
+      </c>
+      <c r="E31">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F31">
+        <v>353.38</v>
+      </c>
+      <c r="G31">
+        <v>353.38</v>
+      </c>
+      <c r="H31">
+        <v>353.38</v>
+      </c>
+      <c r="I31">
+        <v>353.38</v>
+      </c>
+      <c r="J31">
+        <v>353.38</v>
+      </c>
+      <c r="K31">
+        <v>353.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542E2B41-63FB-4917-B589-CEB4BACF0DD5}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>931</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F2">
+        <v>163</v>
+      </c>
+      <c r="G2">
+        <v>163</v>
+      </c>
+      <c r="H2">
+        <v>163</v>
+      </c>
+      <c r="I2">
+        <v>163</v>
+      </c>
+      <c r="J2">
+        <v>163</v>
+      </c>
+      <c r="K2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F3">
+        <v>299.25</v>
+      </c>
+      <c r="G3">
+        <v>299.25</v>
+      </c>
+      <c r="H3">
+        <v>299.25</v>
+      </c>
+      <c r="I3">
+        <v>299.25</v>
+      </c>
+      <c r="J3">
+        <v>299.25</v>
+      </c>
+      <c r="K3">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F4">
+        <v>321.25</v>
+      </c>
+      <c r="G4">
+        <v>321.25</v>
+      </c>
+      <c r="H4">
+        <v>321.25</v>
+      </c>
+      <c r="I4">
+        <v>321.25</v>
+      </c>
+      <c r="J4">
+        <v>321.25</v>
+      </c>
+      <c r="K4">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F5">
+        <v>265.75</v>
+      </c>
+      <c r="G5">
+        <v>265.75</v>
+      </c>
+      <c r="H5">
+        <v>265.75</v>
+      </c>
+      <c r="I5">
+        <v>265.75</v>
+      </c>
+      <c r="J5">
+        <v>265.75</v>
+      </c>
+      <c r="K5">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>3.4</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F6">
+        <v>180.93</v>
+      </c>
+      <c r="G6">
+        <v>180.93</v>
+      </c>
+      <c r="H6">
+        <v>180.93</v>
+      </c>
+      <c r="I6">
+        <v>180.93</v>
+      </c>
+      <c r="J6">
+        <v>180.93</v>
+      </c>
+      <c r="K6">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>293</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F7">
+        <v>353.38</v>
+      </c>
+      <c r="G7">
+        <v>353.38</v>
+      </c>
+      <c r="H7">
+        <v>353.38</v>
+      </c>
+      <c r="I7">
+        <v>353.38</v>
+      </c>
+      <c r="J7">
+        <v>353.38</v>
+      </c>
+      <c r="K7">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8">
+        <v>931</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F8">
+        <v>163</v>
+      </c>
+      <c r="G8">
+        <v>163</v>
+      </c>
+      <c r="H8">
+        <v>163</v>
+      </c>
+      <c r="I8">
+        <v>163</v>
+      </c>
+      <c r="J8">
+        <v>163</v>
+      </c>
+      <c r="K8">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F9">
+        <v>299.25</v>
+      </c>
+      <c r="G9">
+        <v>299.25</v>
+      </c>
+      <c r="H9">
+        <v>299.25</v>
+      </c>
+      <c r="I9">
+        <v>299.25</v>
+      </c>
+      <c r="J9">
+        <v>299.25</v>
+      </c>
+      <c r="K9">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10">
+        <v>42</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F10">
+        <v>321.25</v>
+      </c>
+      <c r="G10">
+        <v>321.25</v>
+      </c>
+      <c r="H10">
+        <v>321.25</v>
+      </c>
+      <c r="I10">
+        <v>321.25</v>
+      </c>
+      <c r="J10">
+        <v>321.25</v>
+      </c>
+      <c r="K10">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <v>110</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F11">
+        <v>265.75</v>
+      </c>
+      <c r="G11">
+        <v>265.75</v>
+      </c>
+      <c r="H11">
+        <v>265.75</v>
+      </c>
+      <c r="I11">
+        <v>265.75</v>
+      </c>
+      <c r="J11">
+        <v>265.75</v>
+      </c>
+      <c r="K11">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12">
+        <v>3.4</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F12">
+        <v>180.93</v>
+      </c>
+      <c r="G12">
+        <v>180.93</v>
+      </c>
+      <c r="H12">
+        <v>180.93</v>
+      </c>
+      <c r="I12">
+        <v>180.93</v>
+      </c>
+      <c r="J12">
+        <v>180.93</v>
+      </c>
+      <c r="K12">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13">
+        <v>293</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F13">
+        <v>353.38</v>
+      </c>
+      <c r="G13">
+        <v>353.38</v>
+      </c>
+      <c r="H13">
+        <v>353.38</v>
+      </c>
+      <c r="I13">
+        <v>353.38</v>
+      </c>
+      <c r="J13">
+        <v>353.38</v>
+      </c>
+      <c r="K13">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>931</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F14">
+        <v>163</v>
+      </c>
+      <c r="G14">
+        <v>163</v>
+      </c>
+      <c r="H14">
+        <v>163</v>
+      </c>
+      <c r="I14">
+        <v>163</v>
+      </c>
+      <c r="J14">
+        <v>163</v>
+      </c>
+      <c r="K14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F15">
+        <v>299.25</v>
+      </c>
+      <c r="G15">
+        <v>299.25</v>
+      </c>
+      <c r="H15">
+        <v>299.25</v>
+      </c>
+      <c r="I15">
+        <v>299.25</v>
+      </c>
+      <c r="J15">
+        <v>299.25</v>
+      </c>
+      <c r="K15">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>42</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F16">
+        <v>321.25</v>
+      </c>
+      <c r="G16">
+        <v>321.25</v>
+      </c>
+      <c r="H16">
+        <v>321.25</v>
+      </c>
+      <c r="I16">
+        <v>321.25</v>
+      </c>
+      <c r="J16">
+        <v>321.25</v>
+      </c>
+      <c r="K16">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>110</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F17">
+        <v>265.75</v>
+      </c>
+      <c r="G17">
+        <v>265.75</v>
+      </c>
+      <c r="H17">
+        <v>265.75</v>
+      </c>
+      <c r="I17">
+        <v>265.75</v>
+      </c>
+      <c r="J17">
+        <v>265.75</v>
+      </c>
+      <c r="K17">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18">
+        <v>3.4</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F18">
+        <v>180.93</v>
+      </c>
+      <c r="G18">
+        <v>180.93</v>
+      </c>
+      <c r="H18">
+        <v>180.93</v>
+      </c>
+      <c r="I18">
+        <v>180.93</v>
+      </c>
+      <c r="J18">
+        <v>180.93</v>
+      </c>
+      <c r="K18">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19">
+        <v>293</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F19">
+        <v>353.38</v>
+      </c>
+      <c r="G19">
+        <v>353.38</v>
+      </c>
+      <c r="H19">
+        <v>353.38</v>
+      </c>
+      <c r="I19">
+        <v>353.38</v>
+      </c>
+      <c r="J19">
+        <v>353.38</v>
+      </c>
+      <c r="K19">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20">
+        <v>931</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F20">
+        <v>163</v>
+      </c>
+      <c r="G20">
+        <v>163</v>
+      </c>
+      <c r="H20">
+        <v>163</v>
+      </c>
+      <c r="I20">
+        <v>163</v>
+      </c>
+      <c r="J20">
+        <v>163</v>
+      </c>
+      <c r="K20">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
+        <v>22</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F21">
+        <v>299.25</v>
+      </c>
+      <c r="G21">
+        <v>299.25</v>
+      </c>
+      <c r="H21">
+        <v>299.25</v>
+      </c>
+      <c r="I21">
+        <v>299.25</v>
+      </c>
+      <c r="J21">
+        <v>299.25</v>
+      </c>
+      <c r="K21">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F22">
+        <v>321.25</v>
+      </c>
+      <c r="G22">
+        <v>321.25</v>
+      </c>
+      <c r="H22">
+        <v>321.25</v>
+      </c>
+      <c r="I22">
+        <v>321.25</v>
+      </c>
+      <c r="J22">
+        <v>321.25</v>
+      </c>
+      <c r="K22">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23">
+        <v>110</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F23">
+        <v>265.75</v>
+      </c>
+      <c r="G23">
+        <v>265.75</v>
+      </c>
+      <c r="H23">
+        <v>265.75</v>
+      </c>
+      <c r="I23">
+        <v>265.75</v>
+      </c>
+      <c r="J23">
+        <v>265.75</v>
+      </c>
+      <c r="K23">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>3.4</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F24">
+        <v>180.93</v>
+      </c>
+      <c r="G24">
+        <v>180.93</v>
+      </c>
+      <c r="H24">
+        <v>180.93</v>
+      </c>
+      <c r="I24">
+        <v>180.93</v>
+      </c>
+      <c r="J24">
+        <v>180.93</v>
+      </c>
+      <c r="K24">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25">
+        <v>293</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>2046.764444444445</v>
+      </c>
+      <c r="F25">
+        <v>353.38</v>
+      </c>
+      <c r="G25">
+        <v>353.38</v>
+      </c>
+      <c r="H25">
+        <v>353.38</v>
+      </c>
+      <c r="I25">
+        <v>353.38</v>
+      </c>
+      <c r="J25">
+        <v>353.38</v>
+      </c>
+      <c r="K25">
+        <v>353.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26">
+        <v>931</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>1100.775555555555</v>
+      </c>
+      <c r="F26">
+        <v>163</v>
+      </c>
+      <c r="G26">
+        <v>163</v>
+      </c>
+      <c r="H26">
+        <v>163</v>
+      </c>
+      <c r="I26">
+        <v>163</v>
+      </c>
+      <c r="J26">
+        <v>163</v>
+      </c>
+      <c r="K26">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>2042.8166666666671</v>
+      </c>
+      <c r="F27">
+        <v>299.25</v>
+      </c>
+      <c r="G27">
+        <v>299.25</v>
+      </c>
+      <c r="H27">
+        <v>299.25</v>
+      </c>
+      <c r="I27">
+        <v>299.25</v>
+      </c>
+      <c r="J27">
+        <v>299.25</v>
+      </c>
+      <c r="K27">
+        <v>299.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28">
+        <v>42</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1184.481111111111</v>
+      </c>
+      <c r="F28">
+        <v>321.25</v>
+      </c>
+      <c r="G28">
+        <v>321.25</v>
+      </c>
+      <c r="H28">
+        <v>321.25</v>
+      </c>
+      <c r="I28">
+        <v>321.25</v>
+      </c>
+      <c r="J28">
+        <v>321.25</v>
+      </c>
+      <c r="K28">
+        <v>321.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29">
+        <v>110</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1127.6288888888889</v>
+      </c>
+      <c r="F29">
+        <v>265.75</v>
+      </c>
+      <c r="G29">
+        <v>265.75</v>
+      </c>
+      <c r="H29">
+        <v>265.75</v>
+      </c>
+      <c r="I29">
+        <v>265.75</v>
+      </c>
+      <c r="J29">
+        <v>265.75</v>
+      </c>
+      <c r="K29">
+        <v>265.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30">
+        <v>3.4</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>2397.3777777777782</v>
+      </c>
+      <c r="F30">
+        <v>180.93</v>
+      </c>
+      <c r="G30">
+        <v>180.93</v>
+      </c>
+      <c r="H30">
+        <v>180.93</v>
+      </c>
+      <c r="I30">
+        <v>180.93</v>
+      </c>
+      <c r="J30">
+        <v>180.93</v>
+      </c>
+      <c r="K30">
+        <v>180.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
+        <v>293</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -3650,7 +4756,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
